--- a/wyniki/miasta_2020_wiecej_niz_100k.xlsx
+++ b/wyniki/miasta_2020_wiecej_niz_100k.xlsx
@@ -541,16 +541,16 @@
         <v>0.7344059942883507</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.049066817406624</v>
+        <v>3.003083134727956</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5956918153421715</v>
+        <v>2.18434069373212</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3057267931527779</v>
+        <v>2.30137221447398</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7344059942883507</v>
+        <v>2.772533242989184</v>
       </c>
     </row>
     <row r="3">
@@ -596,16 +596,16 @@
         <v>0.6061617130259244</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.060757550887966</v>
+        <v>3.011795018045465</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5005003316237947</v>
+        <v>2.064682336450233</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1531149571857127</v>
+        <v>2.189177316749634</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6061617130259244</v>
+        <v>3.160229753597505</v>
       </c>
     </row>
     <row r="4">
@@ -651,16 +651,16 @@
         <v>0.7784236996182913</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.132979915033457</v>
+        <v>3.279254097450729</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01932754951914257</v>
+        <v>1.792630439315734</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3714977141404204</v>
+        <v>1.971865016569028</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7784236996182913</v>
+        <v>3.391643250327918</v>
       </c>
     </row>
     <row r="5">
@@ -706,16 +706,16 @@
         <v>0.6674701030813073</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.115452170106865</v>
+        <v>3.228826488885509</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04805571533991297</v>
+        <v>1.785119842564967</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3879430210508531</v>
+        <v>2.006249121158252</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6674701030813073</v>
+        <v>3.068543775904999</v>
       </c>
     </row>
     <row r="6">
@@ -761,16 +761,16 @@
         <v>0.8619705125717277</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.114328867295981</v>
+        <v>3.226758583173184</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01639317129871607</v>
+        <v>1.804608891897886</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3361943210169882</v>
+        <v>1.912691428227826</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8619705125717277</v>
+        <v>3.453890516437971</v>
       </c>
     </row>
     <row r="7">
@@ -816,16 +816,16 @@
         <v>0.73193982334037</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.115141478995023</v>
+        <v>3.228325235943704</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04611004692723098</v>
+        <v>1.782099717025029</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3846067523378922</v>
+        <v>1.991125772877381</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.73193982334037</v>
+        <v>3.2250649697633</v>
       </c>
     </row>
     <row r="8">
@@ -871,16 +871,16 @@
         <v>0.6999544976020403</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.018479934563874</v>
+        <v>2.426572507389572</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0004166308280419575</v>
+        <v>2.19772091173746</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2270315189148209</v>
+        <v>2.438607873137056</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6999544976020403</v>
+        <v>2.221407898271663</v>
       </c>
     </row>
     <row r="9">
@@ -926,16 +926,16 @@
         <v>0.6290875517192396</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9941107006861473</v>
+        <v>2.409540501466825</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.01639534125963722</v>
+        <v>2.64822396878661</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4732392211044101</v>
+        <v>2.768951768711387</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6290875517192396</v>
+        <v>2.589353331110694</v>
       </c>
     </row>
     <row r="10">
@@ -981,16 +981,16 @@
         <v>-0.1370664561318589</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8828671546536071</v>
+        <v>2.494948058641422</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7410639463480362</v>
+        <v>2.570299636484348</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6575455934006963</v>
+        <v>2.60581584323781</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1370664561318589</v>
+        <v>3.051558627996472</v>
       </c>
     </row>
     <row r="11">
@@ -1036,16 +1036,16 @@
         <v>-0.3461098914395236</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8705969287972414</v>
+        <v>2.43768621569188</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4399710405670009</v>
+        <v>2.583632295399334</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.808920453329772</v>
+        <v>2.760083957225969</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.3461098914395236</v>
+        <v>1.87119618701836</v>
       </c>
     </row>
     <row r="12">
@@ -1091,16 +1091,16 @@
         <v>-0.7111754555068829</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5280642194286289</v>
+        <v>2.487238907425323</v>
       </c>
       <c r="O12" t="n">
-        <v>0.116032944216296</v>
+        <v>2.422863615224073</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2653171215952123</v>
+        <v>2.797771683428288</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.7111754555068829</v>
+        <v>2.578999217701424</v>
       </c>
     </row>
     <row r="13">
@@ -1146,16 +1146,16 @@
         <v>0.6832656775463649</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5232349459257543</v>
+        <v>2.201825020639728</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2646015684190498</v>
+        <v>2.721509611276423</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.7436470793494088</v>
+        <v>2.762426637200995</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.6832656775463649</v>
+        <v>2.607634599009052</v>
       </c>
     </row>
     <row r="14">
@@ -1201,16 +1201,16 @@
         <v>0.3990532045910526</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.965711565042318</v>
+        <v>2.76602019567438</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9796132843539571</v>
+        <v>2.623138050942269</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.8732668564752676</v>
+        <v>2.782243697084627</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3990532045910526</v>
+        <v>2.095556093432787</v>
       </c>
     </row>
     <row r="15">
@@ -1256,16 +1256,16 @@
         <v>1.409681443567515</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6976229252193038</v>
+        <v>2.437787542076092</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1711354874030024</v>
+        <v>2.173474614504102</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6603659358355323</v>
+        <v>2.13455991310403</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.409681443567515</v>
+        <v>4.852904617129614</v>
       </c>
     </row>
     <row r="16">
@@ -1311,16 +1311,16 @@
         <v>0.1530039243119526</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.000137612502554</v>
+        <v>2.350562471971214</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3121221817559333</v>
+        <v>1.922321853402082</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5315165151196716</v>
+        <v>2.237647123374101</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1530039243119526</v>
+        <v>3.354029186353528</v>
       </c>
     </row>
     <row r="17">
@@ -1366,16 +1366,16 @@
         <v>1.149385841852455</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9607792198790635</v>
+        <v>2.57839676933089</v>
       </c>
       <c r="O17" t="n">
-        <v>0.006658417900784676</v>
+        <v>1.800755769135795</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3023720616150244</v>
+        <v>1.945611295400182</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.149385841852455</v>
+        <v>4.716981423440388</v>
       </c>
     </row>
     <row r="18">
@@ -1421,16 +1421,16 @@
         <v>0.9012848413102806</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7531814265145228</v>
+        <v>2.925335767182407</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3935153401708136</v>
+        <v>2.207500384184713</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3344636228824548</v>
+        <v>2.302807011448686</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9012848413102806</v>
+        <v>2.95384286773269</v>
       </c>
     </row>
     <row r="19">
@@ -1476,16 +1476,16 @@
         <v>0.8365150851199669</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8053769142804657</v>
+        <v>2.906986346369173</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3675127179486247</v>
+        <v>2.105255084430556</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2597547840184312</v>
+        <v>2.207883226836254</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.8365150851199669</v>
+        <v>2.88567036869707</v>
       </c>
     </row>
     <row r="20">
@@ -1531,16 +1531,16 @@
         <v>0.7818372402611494</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7131841491021925</v>
+        <v>2.537243500806937</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4189777222340954</v>
+        <v>2.11717147702709</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2806217814794744</v>
+        <v>2.230614539317067</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.7818372402611494</v>
+        <v>2.66428431150459</v>
       </c>
     </row>
     <row r="21">
@@ -1586,16 +1586,16 @@
         <v>0.8831759437912563</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.697200819422293</v>
+        <v>2.529738803742787</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3695508218637346</v>
+        <v>2.06718935263468</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2820435186122353</v>
+        <v>2.226182114577521</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.8831759437912563</v>
+        <v>3.102882035680893</v>
       </c>
     </row>
     <row r="22">
@@ -1641,16 +1641,16 @@
         <v>0.3533115108067598</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6824695243803764</v>
+        <v>2.643024591990387</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6674781559147923</v>
+        <v>2.16102335962512</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3500581895795726</v>
+        <v>1.86522601204831</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.3533115108067598</v>
+        <v>2.478457523188589</v>
       </c>
     </row>
     <row r="23">
@@ -1696,16 +1696,16 @@
         <v>0.09145038353074851</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7813170409391903</v>
+        <v>2.871804424889435</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0835866992882896</v>
+        <v>1.779591679500536</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3540139877864659</v>
+        <v>1.79473826679692</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.09145038353074851</v>
+        <v>2.237952979166879</v>
       </c>
     </row>
     <row r="24">
@@ -1751,16 +1751,16 @@
         <v>1.146127271625788</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.322068821477472</v>
+        <v>3.730041151957919</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5285935940517473</v>
+        <v>4.029643167036653</v>
       </c>
       <c r="P24" t="n">
-        <v>1.629192217921809</v>
+        <v>6.150969875814871</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.146127271625788</v>
+        <v>4.654227654450741</v>
       </c>
     </row>
     <row r="25">
@@ -1806,16 +1806,16 @@
         <v>1.36576317183626</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.8910362721531075</v>
+        <v>2.400306884870819</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.2005985670976532</v>
+        <v>1.702490119002371</v>
       </c>
       <c r="P25" t="n">
-        <v>0.1641538344558121</v>
+        <v>2.009734208379837</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.36576317183626</v>
+        <v>4.823136351863826</v>
       </c>
     </row>
     <row r="26">
@@ -1861,16 +1861,16 @@
         <v>1.346860862545721</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.8910362721531075</v>
+        <v>2.400306884870819</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.2098977032407899</v>
+        <v>1.708490073515179</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1762163279053785</v>
+        <v>2.023062238467871</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.346860862545721</v>
+        <v>4.761825688484106</v>
       </c>
     </row>
     <row r="27">
@@ -1916,16 +1916,16 @@
         <v>0.1951498910222657</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.1081914794529843</v>
+        <v>1.612999175829748</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.4529772279745389</v>
+        <v>2.408875599416044</v>
       </c>
       <c r="P27" t="n">
-        <v>0.4189170470176897</v>
+        <v>2.944338965571226</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.1951498910222657</v>
+        <v>1.589920160387822</v>
       </c>
     </row>
     <row r="28">
@@ -1971,16 +1971,16 @@
         <v>-0.2939321211581569</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.9908735065272789</v>
+        <v>2.333052650131278</v>
       </c>
       <c r="O28" t="n">
-        <v>1.14543775941737</v>
+        <v>4.140506718331365</v>
       </c>
       <c r="P28" t="n">
-        <v>1.632351959328322</v>
+        <v>5.547071639717036</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.2939321211581569</v>
+        <v>1.810915736698733</v>
       </c>
     </row>
     <row r="29">
@@ -2026,16 +2026,16 @@
         <v>-0.2117946169118306</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.9909729252686675</v>
+        <v>2.333534582735432</v>
       </c>
       <c r="O29" t="n">
-        <v>1.054106984061306</v>
+        <v>3.811161872283057</v>
       </c>
       <c r="P29" t="n">
-        <v>1.626866605795178</v>
+        <v>5.519607140398218</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.2117946169118306</v>
+        <v>1.933639990203635</v>
       </c>
     </row>
     <row r="30">
@@ -2081,16 +2081,16 @@
         <v>-0.2314504900749934</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.9908778783768826</v>
+        <v>2.333102106639978</v>
       </c>
       <c r="O30" t="n">
-        <v>1.045935106816891</v>
+        <v>3.731894561396179</v>
       </c>
       <c r="P30" t="n">
-        <v>1.602876243262185</v>
+        <v>5.412199039750849</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.2314504900749934</v>
+        <v>1.929938632897423</v>
       </c>
     </row>
     <row r="31">
@@ -2136,16 +2136,16 @@
         <v>0.1948083312420035</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.9885005935729976</v>
+        <v>2.330707047879031</v>
       </c>
       <c r="O31" t="n">
-        <v>0.8869821565352407</v>
+        <v>3.309610510207322</v>
       </c>
       <c r="P31" t="n">
-        <v>1.501555613224422</v>
+        <v>5.025139028611728</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.1948083312420035</v>
+        <v>2.469458699874234</v>
       </c>
     </row>
     <row r="32">
@@ -2191,16 +2191,16 @@
         <v>-0.1949270710533075</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.9885005935729976</v>
+        <v>2.330707047879031</v>
       </c>
       <c r="O32" t="n">
-        <v>1.085951184647078</v>
+        <v>3.845113986456313</v>
       </c>
       <c r="P32" t="n">
-        <v>1.57516485331511</v>
+        <v>5.297408053366642</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.1949270710533075</v>
+        <v>2.221189084792347</v>
       </c>
     </row>
     <row r="33">
@@ -2246,16 +2246,16 @@
         <v>0.5105751344764587</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.98923675812668</v>
+        <v>2.332886081642056</v>
       </c>
       <c r="O33" t="n">
-        <v>0.4647848334094689</v>
+        <v>2.127437700977174</v>
       </c>
       <c r="P33" t="n">
-        <v>1.218168052910355</v>
+        <v>3.993138595118903</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.5105751344764587</v>
+        <v>3.107278600974586</v>
       </c>
     </row>
     <row r="34">
@@ -2301,16 +2301,16 @@
         <v>0.5681665245323665</v>
       </c>
       <c r="N34" t="n">
-        <v>-0.989451037552099</v>
+        <v>2.332973237618096</v>
       </c>
       <c r="O34" t="n">
-        <v>0.4442140962041584</v>
+        <v>1.949107665499704</v>
       </c>
       <c r="P34" t="n">
-        <v>1.165404207449193</v>
+        <v>3.773618755990293</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.5681665245323665</v>
+        <v>3.274343182631906</v>
       </c>
     </row>
     <row r="35">
@@ -2356,16 +2356,16 @@
         <v>0.5034432166113471</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.989451037552099</v>
+        <v>2.332973237618096</v>
       </c>
       <c r="O35" t="n">
-        <v>0.4153480141521155</v>
+        <v>1.986800034376624</v>
       </c>
       <c r="P35" t="n">
-        <v>1.183716650086601</v>
+        <v>3.865791949756356</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.5034432166113471</v>
+        <v>3.08961068682083</v>
       </c>
     </row>
     <row r="36">
@@ -2411,16 +2411,16 @@
         <v>0.6769265794224752</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.9895354486670873</v>
+        <v>2.332666324992664</v>
       </c>
       <c r="O36" t="n">
-        <v>0.5268065109151658</v>
+        <v>1.954054866810678</v>
       </c>
       <c r="P36" t="n">
-        <v>1.165740988513726</v>
+        <v>3.704276656697934</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.6769265794224752</v>
+        <v>3.644158088562285</v>
       </c>
     </row>
     <row r="37">
@@ -2466,16 +2466,16 @@
         <v>-0.05781481470519394</v>
       </c>
       <c r="N37" t="n">
-        <v>-1.040645078252044</v>
+        <v>3.186262086577424</v>
       </c>
       <c r="O37" t="n">
-        <v>0.3359606929942677</v>
+        <v>3.256739505430045</v>
       </c>
       <c r="P37" t="n">
-        <v>0.3705684652414726</v>
+        <v>3.344914752480311</v>
       </c>
       <c r="Q37" t="n">
-        <v>-0.05781481470519394</v>
+        <v>2.922678422151212</v>
       </c>
     </row>
     <row r="38">
@@ -2521,16 +2521,16 @@
         <v>0.9833384489534706</v>
       </c>
       <c r="N38" t="n">
-        <v>-1.027094967844414</v>
+        <v>2.758813973339101</v>
       </c>
       <c r="O38" t="n">
-        <v>-0.1240077882578537</v>
+        <v>2.584480208808581</v>
       </c>
       <c r="P38" t="n">
-        <v>-0.692529986843491</v>
+        <v>2.863537686809754</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.9833384489534706</v>
+        <v>2.689640195859509</v>
       </c>
     </row>
     <row r="39">
@@ -2576,16 +2576,16 @@
         <v>0.2791048000282301</v>
       </c>
       <c r="N39" t="n">
-        <v>-0.2564250724241893</v>
+        <v>1.885163921537938</v>
       </c>
       <c r="O39" t="n">
-        <v>-0.5885423556902428</v>
+        <v>2.49842532174323</v>
       </c>
       <c r="P39" t="n">
-        <v>0.3081659979818125</v>
+        <v>3.044628481950695</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.2791048000282301</v>
+        <v>1.500755646495114</v>
       </c>
     </row>
     <row r="40">
@@ -2631,16 +2631,16 @@
         <v>0.4897115238975082</v>
       </c>
       <c r="N40" t="n">
-        <v>-0.5105784118566823</v>
+        <v>2.521404324629664</v>
       </c>
       <c r="O40" t="n">
-        <v>-0.09275174988182648</v>
+        <v>1.978214180953024</v>
       </c>
       <c r="P40" t="n">
-        <v>0.3391551684638875</v>
+        <v>1.913385763098365</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.4897115238975082</v>
+        <v>2.14561483128057</v>
       </c>
     </row>
     <row r="41">
@@ -2686,16 +2686,16 @@
         <v>0.4800118907413978</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.5181892637460837</v>
+        <v>2.600142115419443</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.01979452971796531</v>
+        <v>1.976842664657278</v>
       </c>
       <c r="P41" t="n">
-        <v>0.3490993631520517</v>
+        <v>1.914341175873128</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.4800118907413978</v>
+        <v>2.106239845782597</v>
       </c>
     </row>
     <row r="42">
@@ -2741,16 +2741,16 @@
         <v>0.2830580551551284</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.5757440996456897</v>
+        <v>2.35252930635441</v>
       </c>
       <c r="O42" t="n">
-        <v>0.2236339957245468</v>
+        <v>2.468107038920782</v>
       </c>
       <c r="P42" t="n">
-        <v>0.4350580644790016</v>
+        <v>2.799646035497925</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.2830580551551284</v>
+        <v>1.682048894982178</v>
       </c>
     </row>
     <row r="43">
@@ -2796,16 +2796,16 @@
         <v>0.5679566252625926</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.6190577743052601</v>
+        <v>2.321373622064474</v>
       </c>
       <c r="O43" t="n">
-        <v>0.1630884694442475</v>
+        <v>2.435469214587017</v>
       </c>
       <c r="P43" t="n">
-        <v>0.4403339241665433</v>
+        <v>2.919179965552041</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.5679566252625926</v>
+        <v>2.116855046556154</v>
       </c>
     </row>
     <row r="44">
@@ -2851,16 +2851,16 @@
         <v>0.2491540883240657</v>
       </c>
       <c r="N44" t="n">
-        <v>0.7545235919482758</v>
+        <v>4.094762419738207</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.3565487387459741</v>
+        <v>2.124710166873139</v>
       </c>
       <c r="P44" t="n">
-        <v>0.2157586946354396</v>
+        <v>2.11165491265692</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.2491540883240657</v>
+        <v>3.011086261905167</v>
       </c>
     </row>
     <row r="45">
@@ -2906,16 +2906,16 @@
         <v>-0.139599735126138</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.9175812612824273</v>
+        <v>2.441775550506389</v>
       </c>
       <c r="O45" t="n">
-        <v>-0.9708716233201823</v>
+        <v>3.107837262339618</v>
       </c>
       <c r="P45" t="n">
-        <v>-1.029638319883593</v>
+        <v>3.112400036381231</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.139599735126138</v>
+        <v>1.744050855483409</v>
       </c>
     </row>
     <row r="46">
@@ -2961,16 +2961,16 @@
         <v>0.1301211741003858</v>
       </c>
       <c r="N46" t="n">
-        <v>-0.002049860558356992</v>
+        <v>1.652236508521947</v>
       </c>
       <c r="O46" t="n">
-        <v>0.5360988864290024</v>
+        <v>2.020458006307718</v>
       </c>
       <c r="P46" t="n">
-        <v>0.7210003750197925</v>
+        <v>2.233086484934058</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.1301211741003858</v>
+        <v>2.891213915394045</v>
       </c>
     </row>
     <row r="47">
@@ -3016,16 +3016,16 @@
         <v>0.0338451498315072</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.002049860558356992</v>
+        <v>1.652236508521947</v>
       </c>
       <c r="O47" t="n">
-        <v>0.6249454556168602</v>
+        <v>2.232745688375034</v>
       </c>
       <c r="P47" t="n">
-        <v>0.7275546492089204</v>
+        <v>2.21755471891084</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.0338451498315072</v>
+        <v>2.849509889830462</v>
       </c>
     </row>
     <row r="48">
@@ -3071,16 +3071,16 @@
         <v>0.06765287628925241</v>
       </c>
       <c r="N48" t="n">
-        <v>-1.005609785896745</v>
+        <v>2.733278555639851</v>
       </c>
       <c r="O48" t="n">
-        <v>-0.7054458661671655</v>
+        <v>2.655048365573256</v>
       </c>
       <c r="P48" t="n">
-        <v>-0.9801607894122089</v>
+        <v>2.993472571394467</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.06765287628925241</v>
+        <v>2.587788553229296</v>
       </c>
     </row>
     <row r="49">
@@ -3126,16 +3126,16 @@
         <v>-0.227167183955121</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.9039623541878529</v>
+        <v>2.358839336228421</v>
       </c>
       <c r="O49" t="n">
-        <v>0.834342593997244</v>
+        <v>3.395459283402795</v>
       </c>
       <c r="P49" t="n">
-        <v>1.572275228377737</v>
+        <v>5.399657549510763</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.227167183955121</v>
+        <v>1.961257417772988</v>
       </c>
     </row>
     <row r="50">
@@ -3181,16 +3181,16 @@
         <v>0.5950262186851886</v>
       </c>
       <c r="N50" t="n">
-        <v>-0.1586728253047582</v>
+        <v>1.777025394766274</v>
       </c>
       <c r="O50" t="n">
-        <v>0.3825412151609865</v>
+        <v>1.932012335797671</v>
       </c>
       <c r="P50" t="n">
-        <v>0.6847264711287877</v>
+        <v>2.34697092516961</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.5950262186851886</v>
+        <v>1.980177379315019</v>
       </c>
     </row>
     <row r="51">
@@ -3236,16 +3236,16 @@
         <v>0.6050681938100543</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.158852361961215</v>
+        <v>1.776082692715691</v>
       </c>
       <c r="O51" t="n">
-        <v>0.3970421992341321</v>
+        <v>2.012473939274128</v>
       </c>
       <c r="P51" t="n">
-        <v>0.7018385907223833</v>
+        <v>2.40883587052298</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.6050681938100543</v>
+        <v>1.962904279476088</v>
       </c>
     </row>
     <row r="52">
@@ -3291,16 +3291,16 @@
         <v>0.6036509692513147</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.4942146579682675</v>
+        <v>2.159960840321855</v>
       </c>
       <c r="O52" t="n">
-        <v>0.4500174430912974</v>
+        <v>2.050140223529052</v>
       </c>
       <c r="P52" t="n">
-        <v>0.7709416704976304</v>
+        <v>2.579431140404438</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.6036509692513147</v>
+        <v>2.041825611904194</v>
       </c>
     </row>
     <row r="53">
@@ -3346,16 +3346,16 @@
         <v>0.4048571779561919</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.4868939928034084</v>
+        <v>2.164545437656697</v>
       </c>
       <c r="O53" t="n">
-        <v>0.371046890494692</v>
+        <v>2.028121048046619</v>
       </c>
       <c r="P53" t="n">
-        <v>0.6788668259515908</v>
+        <v>2.483307657460356</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.4048571779561919</v>
+        <v>1.62494119159372</v>
       </c>
     </row>
     <row r="54">
@@ -3401,16 +3401,16 @@
         <v>0.6246812817853693</v>
       </c>
       <c r="N54" t="n">
-        <v>-0.5017301989037382</v>
+        <v>2.169283221485765</v>
       </c>
       <c r="O54" t="n">
-        <v>0.346689957554725</v>
+        <v>1.98088953859203</v>
       </c>
       <c r="P54" t="n">
-        <v>0.708747321278807</v>
+        <v>2.483385807854902</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.6246812817853693</v>
+        <v>2.053728802569616</v>
       </c>
     </row>
     <row r="55">
@@ -3456,16 +3456,16 @@
         <v>0.6095505015069452</v>
       </c>
       <c r="N55" t="n">
-        <v>-0.5009988702086487</v>
+        <v>2.171084016683281</v>
       </c>
       <c r="O55" t="n">
-        <v>0.340936346038489</v>
+        <v>1.972879422951236</v>
       </c>
       <c r="P55" t="n">
-        <v>0.6985846257392148</v>
+        <v>2.466242803822359</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.6095505015069452</v>
+        <v>2.015171301387867</v>
       </c>
     </row>
     <row r="56">
@@ -3511,16 +3511,16 @@
         <v>0.5061329232788465</v>
       </c>
       <c r="N56" t="n">
-        <v>-0.5024983645033044</v>
+        <v>2.171814967978321</v>
       </c>
       <c r="O56" t="n">
-        <v>0.4058654752376784</v>
+        <v>2.078169886991171</v>
       </c>
       <c r="P56" t="n">
-        <v>0.7284313238216079</v>
+        <v>2.604290062538128</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.5061329232788465</v>
+        <v>1.886074250972565</v>
       </c>
     </row>
     <row r="57">
@@ -3566,16 +3566,16 @@
         <v>0.4558344847695674</v>
       </c>
       <c r="N57" t="n">
-        <v>-0.5024983645033044</v>
+        <v>2.171814967978321</v>
       </c>
       <c r="O57" t="n">
-        <v>0.3945739262459462</v>
+        <v>2.038731109746925</v>
       </c>
       <c r="P57" t="n">
-        <v>0.7007301694107241</v>
+        <v>2.505738368883156</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.4558344847695674</v>
+        <v>1.764253195633378</v>
       </c>
     </row>
     <row r="58">
@@ -3621,16 +3621,16 @@
         <v>-0.09384245300893547</v>
       </c>
       <c r="N58" t="n">
-        <v>0.04310132285506618</v>
+        <v>1.613421266598701</v>
       </c>
       <c r="O58" t="n">
-        <v>0.5893153484844039</v>
+        <v>2.17063680132019</v>
       </c>
       <c r="P58" t="n">
-        <v>0.6422293885296428</v>
+        <v>2.146606113489083</v>
       </c>
       <c r="Q58" t="n">
-        <v>-0.09384245300893547</v>
+        <v>3.18629723773967</v>
       </c>
     </row>
     <row r="59">
@@ -3676,16 +3676,16 @@
         <v>-0.02279708928313098</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.792855652184554</v>
+        <v>2.449737593641211</v>
       </c>
       <c r="O59" t="n">
-        <v>-0.1265703062542334</v>
+        <v>2.179984816961418</v>
       </c>
       <c r="P59" t="n">
-        <v>-0.539121427583573</v>
+        <v>2.348651917736429</v>
       </c>
       <c r="Q59" t="n">
-        <v>-0.02279708928313098</v>
+        <v>1.838802769931334</v>
       </c>
     </row>
     <row r="60">
@@ -3731,16 +3731,16 @@
         <v>0.3232707394839504</v>
       </c>
       <c r="N60" t="n">
-        <v>-0.8234531911336488</v>
+        <v>2.44409530445059</v>
       </c>
       <c r="O60" t="n">
-        <v>0.2098847748452149</v>
+        <v>2.658777790284852</v>
       </c>
       <c r="P60" t="n">
-        <v>0.5391843262146678</v>
+        <v>3.149405037890442</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.3232707394839504</v>
+        <v>1.67917470340595</v>
       </c>
     </row>
     <row r="61">
@@ -3786,16 +3786,16 @@
         <v>0.2444072162567809</v>
       </c>
       <c r="N61" t="n">
-        <v>-1.178585403012828</v>
+        <v>3.524286278460648</v>
       </c>
       <c r="O61" t="n">
-        <v>1.874702380485353</v>
+        <v>6.450971851408446</v>
       </c>
       <c r="P61" t="n">
-        <v>1.917933066313428</v>
+        <v>7.059191892262293</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.2444072162567809</v>
+        <v>2.139919381296481</v>
       </c>
     </row>
     <row r="62">
@@ -3841,16 +3841,16 @@
         <v>-0.6044940212655951</v>
       </c>
       <c r="N62" t="n">
-        <v>-0.7204044054869163</v>
+        <v>2.274164360523043</v>
       </c>
       <c r="O62" t="n">
-        <v>-0.4307670268184355</v>
+        <v>2.34094371419103</v>
       </c>
       <c r="P62" t="n">
-        <v>0.1125263295737602</v>
+        <v>3.146564698403308</v>
       </c>
       <c r="Q62" t="n">
-        <v>-0.6044940212655951</v>
+        <v>2.707870447333582</v>
       </c>
     </row>
     <row r="63">
@@ -3896,16 +3896,16 @@
         <v>0.1169696354624688</v>
       </c>
       <c r="N63" t="n">
-        <v>-0.7623011673810767</v>
+        <v>2.604423158046376</v>
       </c>
       <c r="O63" t="n">
-        <v>0.2233660043092022</v>
+        <v>2.395025528339167</v>
       </c>
       <c r="P63" t="n">
-        <v>0.2678880613370935</v>
+        <v>2.279796835348544</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.1169696354624688</v>
+        <v>2.632163170134962</v>
       </c>
     </row>
     <row r="64">
@@ -3951,16 +3951,16 @@
         <v>0.2855176210653022</v>
       </c>
       <c r="N64" t="n">
-        <v>0.6694255621159219</v>
+        <v>1.876636036867283</v>
       </c>
       <c r="O64" t="n">
-        <v>-0.2020444394044871</v>
+        <v>2.412138557821919</v>
       </c>
       <c r="P64" t="n">
-        <v>-0.03014723350181308</v>
+        <v>2.626529525315156</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.2855176210653022</v>
+        <v>3.106158667674592</v>
       </c>
     </row>
     <row r="65">
@@ -4006,16 +4006,16 @@
         <v>1.251248915238648</v>
       </c>
       <c r="N65" t="n">
-        <v>-0.07647084931069922</v>
+        <v>1.626969163204295</v>
       </c>
       <c r="O65" t="n">
-        <v>-0.007519713128337525</v>
+        <v>2.311930515315193</v>
       </c>
       <c r="P65" t="n">
-        <v>0.6793990737633862</v>
+        <v>2.812609631449813</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.251248915238648</v>
+        <v>4.372224658600149</v>
       </c>
     </row>
     <row r="66">
@@ -4061,16 +4061,16 @@
         <v>-0.3655221193726412</v>
       </c>
       <c r="N66" t="n">
-        <v>-0.656159135495848</v>
+        <v>2.643183585101624</v>
       </c>
       <c r="O66" t="n">
-        <v>-0.6548881926783455</v>
+        <v>2.396513998331162</v>
       </c>
       <c r="P66" t="n">
-        <v>-0.4480782798633459</v>
+        <v>2.357860483433804</v>
       </c>
       <c r="Q66" t="n">
-        <v>-0.3655221193726412</v>
+        <v>1.463204308142017</v>
       </c>
     </row>
     <row r="67">
@@ -4116,16 +4116,16 @@
         <v>0.5489734488918175</v>
       </c>
       <c r="N67" t="n">
-        <v>-0.741363436809464</v>
+        <v>2.44862681682353</v>
       </c>
       <c r="O67" t="n">
-        <v>2.404231934703709</v>
+        <v>8.342896267897711</v>
       </c>
       <c r="P67" t="n">
-        <v>1.210802220622642</v>
+        <v>4.290994108178429</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.5489734488918175</v>
+        <v>1.97536998549074</v>
       </c>
     </row>
     <row r="68">
@@ -4171,16 +4171,16 @@
         <v>0.5383716625321517</v>
       </c>
       <c r="N68" t="n">
-        <v>-0.7414128708650018</v>
+        <v>2.448238082786365</v>
       </c>
       <c r="O68" t="n">
-        <v>2.302709155314812</v>
+        <v>7.958603119249144</v>
       </c>
       <c r="P68" t="n">
-        <v>0.9780934168920251</v>
+        <v>3.653886018622676</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.5383716625321517</v>
+        <v>1.832837549044595</v>
       </c>
     </row>
     <row r="69">
@@ -4226,16 +4226,16 @@
         <v>1.00522408834437</v>
       </c>
       <c r="N69" t="n">
-        <v>-0.3100716861012086</v>
+        <v>1.96835268025891</v>
       </c>
       <c r="O69" t="n">
-        <v>-0.03524221996029878</v>
+        <v>2.279275787062712</v>
       </c>
       <c r="P69" t="n">
-        <v>0.6973706632105816</v>
+        <v>2.935857018436778</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.00522408834437</v>
+        <v>3.310567838837478</v>
       </c>
     </row>
     <row r="70">
@@ -4281,16 +4281,16 @@
         <v>1.229471496391012</v>
       </c>
       <c r="N70" t="n">
-        <v>-0.3139256991265609</v>
+        <v>1.997568767933138</v>
       </c>
       <c r="O70" t="n">
-        <v>-0.1339663107513727</v>
+        <v>2.244283627103324</v>
       </c>
       <c r="P70" t="n">
-        <v>0.605261523581417</v>
+        <v>3.061114498856556</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.229471496391012</v>
+        <v>4.18725457048479</v>
       </c>
     </row>
     <row r="71">
@@ -4336,16 +4336,16 @@
         <v>0.7537353843438143</v>
       </c>
       <c r="N71" t="n">
-        <v>-1.217524779668965</v>
+        <v>3.36157992378718</v>
       </c>
       <c r="O71" t="n">
-        <v>-0.4220526197414715</v>
+        <v>1.956480407838838</v>
       </c>
       <c r="P71" t="n">
-        <v>-0.01228620945626703</v>
+        <v>1.612960433171629</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.7537353843438143</v>
+        <v>2.424015834537428</v>
       </c>
     </row>
     <row r="72">
@@ -4391,16 +4391,16 @@
         <v>-0.4759298172264846</v>
       </c>
       <c r="N72" t="n">
-        <v>-0.3179579346542331</v>
+        <v>1.90109766881732</v>
       </c>
       <c r="O72" t="n">
-        <v>-0.1127659444023863</v>
+        <v>2.553162745757101</v>
       </c>
       <c r="P72" t="n">
-        <v>0.09675888328807941</v>
+        <v>2.325394229451294</v>
       </c>
       <c r="Q72" t="n">
-        <v>-0.4759298172264846</v>
+        <v>1.928052741933923</v>
       </c>
     </row>
     <row r="73">
@@ -4446,16 +4446,16 @@
         <v>-0.115819939087826</v>
       </c>
       <c r="N73" t="n">
-        <v>-0.3244560745048231</v>
+        <v>1.909104425591376</v>
       </c>
       <c r="O73" t="n">
-        <v>-0.1972742986623495</v>
+        <v>2.588112120605047</v>
       </c>
       <c r="P73" t="n">
-        <v>0.04323024652571676</v>
+        <v>2.349735205816683</v>
       </c>
       <c r="Q73" t="n">
-        <v>-0.115819939087826</v>
+        <v>1.991758003535792</v>
       </c>
     </row>
     <row r="74">
@@ -4501,16 +4501,16 @@
         <v>-0.038830383388897</v>
       </c>
       <c r="N74" t="n">
-        <v>-0.877059565438725</v>
+        <v>2.374374972196483</v>
       </c>
       <c r="O74" t="n">
-        <v>-0.584904157240153</v>
+        <v>2.426408083460341</v>
       </c>
       <c r="P74" t="n">
-        <v>-0.5260268843054976</v>
+        <v>2.312500033076798</v>
       </c>
       <c r="Q74" t="n">
-        <v>-0.038830383388897</v>
+        <v>1.910658059647285</v>
       </c>
     </row>
     <row r="75">
@@ -4556,16 +4556,16 @@
         <v>0.7869255435868873</v>
       </c>
       <c r="N75" t="n">
-        <v>-1.352590013244649</v>
+        <v>3.62942641278083</v>
       </c>
       <c r="O75" t="n">
-        <v>-0.385371670402213</v>
+        <v>1.904828592665586</v>
       </c>
       <c r="P75" t="n">
-        <v>0.2212342657440717</v>
+        <v>1.977749105826059</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.7869255435868873</v>
+        <v>2.459615330136532</v>
       </c>
     </row>
     <row r="76">
@@ -4611,16 +4611,16 @@
         <v>1.268001451733802</v>
       </c>
       <c r="N76" t="n">
-        <v>-1.391655737608116</v>
+        <v>3.6720641251231</v>
       </c>
       <c r="O76" t="n">
-        <v>0.03583827422096053</v>
+        <v>2.166414076017481</v>
       </c>
       <c r="P76" t="n">
-        <v>0.08271224610029033</v>
+        <v>2.189797377302434</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.268001451733802</v>
+        <v>4.225382507600193</v>
       </c>
     </row>
     <row r="77">
@@ -4666,16 +4666,16 @@
         <v>-0.2810148045947984</v>
       </c>
       <c r="N77" t="n">
-        <v>-0.9421163113695773</v>
+        <v>2.477073205492701</v>
       </c>
       <c r="O77" t="n">
-        <v>-0.6927555570053315</v>
+        <v>2.626864521749557</v>
       </c>
       <c r="P77" t="n">
-        <v>-0.7253750311744163</v>
+        <v>2.635786396568722</v>
       </c>
       <c r="Q77" t="n">
-        <v>-0.2810148045947984</v>
+        <v>2.012188302248939</v>
       </c>
     </row>
     <row r="78">
@@ -4721,16 +4721,16 @@
         <v>0.5789592905480527</v>
       </c>
       <c r="N78" t="n">
-        <v>-1.422057361950495</v>
+        <v>3.731051819887883</v>
       </c>
       <c r="O78" t="n">
-        <v>-0.05469000201449547</v>
+        <v>2.141740160269798</v>
       </c>
       <c r="P78" t="n">
-        <v>0.2854290239646654</v>
+        <v>2.31315235747934</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.5789592905480527</v>
+        <v>2.85549720175879</v>
       </c>
     </row>
     <row r="79">
@@ -4776,16 +4776,16 @@
         <v>0.3778556204038448</v>
       </c>
       <c r="N79" t="n">
-        <v>-1.437468877314801</v>
+        <v>3.755703109198549</v>
       </c>
       <c r="O79" t="n">
-        <v>0.0009165108411421839</v>
+        <v>2.117129020831189</v>
       </c>
       <c r="P79" t="n">
-        <v>0.2826817813791923</v>
+        <v>2.248089747722044</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.3778556204038448</v>
+        <v>2.569043403229461</v>
       </c>
     </row>
     <row r="80">
@@ -4831,16 +4831,16 @@
         <v>0.7225477480944391</v>
       </c>
       <c r="N80" t="n">
-        <v>-1.437468877314801</v>
+        <v>3.755703109198549</v>
       </c>
       <c r="O80" t="n">
-        <v>-0.05627542734057945</v>
+        <v>2.287908726072418</v>
       </c>
       <c r="P80" t="n">
-        <v>0.2843068809990071</v>
+        <v>2.391377569890464</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.7225477480944391</v>
+        <v>3.362391941346583</v>
       </c>
     </row>
     <row r="81">
@@ -4886,16 +4886,16 @@
         <v>0.3351601351880695</v>
       </c>
       <c r="N81" t="n">
-        <v>-1.431969082473425</v>
+        <v>3.748252912460334</v>
       </c>
       <c r="O81" t="n">
-        <v>0.0190520021507869</v>
+        <v>2.121279949102558</v>
       </c>
       <c r="P81" t="n">
-        <v>0.2615460687570923</v>
+        <v>2.157854019738588</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.3351601351880695</v>
+        <v>2.399327806419388</v>
       </c>
     </row>
     <row r="82">
@@ -4941,16 +4941,16 @@
         <v>-0.008119392991955418</v>
       </c>
       <c r="N82" t="n">
-        <v>-0.8056954472770951</v>
+        <v>3.490457137954137</v>
       </c>
       <c r="O82" t="n">
-        <v>0.1295032394854588</v>
+        <v>2.197775479675486</v>
       </c>
       <c r="P82" t="n">
-        <v>0.5620261117035602</v>
+        <v>3.198051240033974</v>
       </c>
       <c r="Q82" t="n">
-        <v>-0.008119392991955418</v>
+        <v>1.872736537854099</v>
       </c>
     </row>
     <row r="83">
@@ -4996,16 +4996,16 @@
         <v>0.8546339381383875</v>
       </c>
       <c r="N83" t="n">
-        <v>0.8536179896781041</v>
+        <v>2.520761664889367</v>
       </c>
       <c r="O83" t="n">
-        <v>-0.1474075721856397</v>
+        <v>2.374627389310824</v>
       </c>
       <c r="P83" t="n">
-        <v>0.08370465559218331</v>
+        <v>2.617779409569294</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.8546339381383875</v>
+        <v>2.658655550630197</v>
       </c>
     </row>
     <row r="84">
@@ -5051,16 +5051,16 @@
         <v>0.6838366978577469</v>
       </c>
       <c r="N84" t="n">
-        <v>0.837498831895482</v>
+        <v>2.491678306030983</v>
       </c>
       <c r="O84" t="n">
-        <v>-0.1664330447737368</v>
+        <v>2.490830826559754</v>
       </c>
       <c r="P84" t="n">
-        <v>0.130194516285231</v>
+        <v>2.678915760174945</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.6838366978577469</v>
+        <v>2.683188905156265</v>
       </c>
     </row>
     <row r="85">
@@ -5106,16 +5106,16 @@
         <v>-0.5604137317126339</v>
       </c>
       <c r="N85" t="n">
-        <v>-0.6693066995763194</v>
+        <v>2.124376575769435</v>
       </c>
       <c r="O85" t="n">
-        <v>-0.2303527282336212</v>
+        <v>1.95976638982749</v>
       </c>
       <c r="P85" t="n">
-        <v>-0.009085961850701324</v>
+        <v>1.794930708905099</v>
       </c>
       <c r="Q85" t="n">
-        <v>-0.5604137317126339</v>
+        <v>2.668569584075295</v>
       </c>
     </row>
     <row r="86">
@@ -5161,16 +5161,16 @@
         <v>-0.06128924535092281</v>
       </c>
       <c r="N86" t="n">
-        <v>-0.6938484406697155</v>
+        <v>2.665765144878233</v>
       </c>
       <c r="O86" t="n">
-        <v>-0.9011241380165143</v>
+        <v>2.855914734016928</v>
       </c>
       <c r="P86" t="n">
-        <v>-0.9733250090021782</v>
+        <v>2.895676022805811</v>
       </c>
       <c r="Q86" t="n">
-        <v>-0.06128924535092281</v>
+        <v>1.244902190289655</v>
       </c>
     </row>
     <row r="87">
@@ -5216,16 +5216,16 @@
         <v>0.131749347551708</v>
       </c>
       <c r="N87" t="n">
-        <v>-0.9749344175540494</v>
+        <v>2.664796203827297</v>
       </c>
       <c r="O87" t="n">
-        <v>0.03463100528286468</v>
+        <v>2.353674177932604</v>
       </c>
       <c r="P87" t="n">
-        <v>0.1081431330472299</v>
+        <v>3.012181661297894</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.131749347551708</v>
+        <v>2.219549853150129</v>
       </c>
     </row>
     <row r="88">
@@ -5271,16 +5271,16 @@
         <v>0.2836294082391205</v>
       </c>
       <c r="N88" t="n">
-        <v>-0.8818961459859452</v>
+        <v>2.569532101646016</v>
       </c>
       <c r="O88" t="n">
-        <v>0.7134791977773054</v>
+        <v>2.727731785886112</v>
       </c>
       <c r="P88" t="n">
-        <v>1.082707792889973</v>
+        <v>3.804169716404215</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.2836294082391205</v>
+        <v>2.570948904563386</v>
       </c>
     </row>
     <row r="89">
@@ -5326,16 +5326,16 @@
         <v>0.3642187011173217</v>
       </c>
       <c r="N89" t="n">
-        <v>-0.4859729664992654</v>
+        <v>2.38556364934287</v>
       </c>
       <c r="O89" t="n">
-        <v>-0.2135073880990377</v>
+        <v>1.972762133601682</v>
       </c>
       <c r="P89" t="n">
-        <v>0.08648449726441645</v>
+        <v>1.978709746994656</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.3642187011173217</v>
+        <v>2.656330252063989</v>
       </c>
     </row>
     <row r="90">
@@ -5381,16 +5381,16 @@
         <v>1.019116775620115</v>
       </c>
       <c r="N90" t="n">
-        <v>0.5945472422639759</v>
+        <v>2.241047394919714</v>
       </c>
       <c r="O90" t="n">
-        <v>-0.5569869794063461</v>
+        <v>2.434847101649141</v>
       </c>
       <c r="P90" t="n">
-        <v>0.5260161126219421</v>
+        <v>3.321564435277276</v>
       </c>
       <c r="Q90" t="n">
-        <v>1.019116775620115</v>
+        <v>3.362594935086174</v>
       </c>
     </row>
     <row r="91">
@@ -5436,16 +5436,16 @@
         <v>0.6834477099527145</v>
       </c>
       <c r="N91" t="n">
-        <v>-0.9427293768233868</v>
+        <v>2.656451831284001</v>
       </c>
       <c r="O91" t="n">
-        <v>0.07599023909327715</v>
+        <v>1.709788697914009</v>
       </c>
       <c r="P91" t="n">
-        <v>0.01145152549412565</v>
+        <v>1.716716641531034</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.6834477099527145</v>
+        <v>3.26634092281056</v>
       </c>
     </row>
     <row r="92">
@@ -5491,16 +5491,16 @@
         <v>0.3113225199090076</v>
       </c>
       <c r="N92" t="n">
-        <v>-0.5044417542223344</v>
+        <v>2.356734150065148</v>
       </c>
       <c r="O92" t="n">
-        <v>0.2216472445956709</v>
+        <v>1.466748658988711</v>
       </c>
       <c r="P92" t="n">
-        <v>0.719103841313976</v>
+        <v>2.315417565437659</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.3113225199090076</v>
+        <v>2.242926296693574</v>
       </c>
     </row>
     <row r="93">
@@ -5546,16 +5546,16 @@
         <v>0.9572396357514158</v>
       </c>
       <c r="N93" t="n">
-        <v>-0.3670968665493964</v>
+        <v>1.931078782737218</v>
       </c>
       <c r="O93" t="n">
-        <v>0.002984267359247307</v>
+        <v>1.753064535365543</v>
       </c>
       <c r="P93" t="n">
-        <v>0.447066349315587</v>
+        <v>1.905895951758114</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.9572396357514158</v>
+        <v>3.636829121256593</v>
       </c>
     </row>
     <row r="94">
@@ -5601,16 +5601,16 @@
         <v>0.3542690710139792</v>
       </c>
       <c r="N94" t="n">
-        <v>-0.2384698614353859</v>
+        <v>2.396826297213791</v>
       </c>
       <c r="O94" t="n">
-        <v>0.2675276457116544</v>
+        <v>2.219805196464571</v>
       </c>
       <c r="P94" t="n">
-        <v>-0.4379736659667559</v>
+        <v>2.54291936715611</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.3542690710139792</v>
+        <v>1.807156058640729</v>
       </c>
     </row>
     <row r="95">
@@ -5656,16 +5656,16 @@
         <v>0.1093887140910247</v>
       </c>
       <c r="N95" t="n">
-        <v>0.1575357012058876</v>
+        <v>2.345492174065459</v>
       </c>
       <c r="O95" t="n">
-        <v>-0.7584750873064861</v>
+        <v>2.878001086077087</v>
       </c>
       <c r="P95" t="n">
-        <v>-1.078524391222329</v>
+        <v>2.998290577109664</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.1093887140910247</v>
+        <v>1.399441031066956</v>
       </c>
     </row>
     <row r="96">
@@ -5711,16 +5711,16 @@
         <v>0.1012331075083175</v>
       </c>
       <c r="N96" t="n">
-        <v>-0.4171986859353459</v>
+        <v>1.761979929818544</v>
       </c>
       <c r="O96" t="n">
-        <v>-0.9074566158574651</v>
+        <v>2.583578498654515</v>
       </c>
       <c r="P96" t="n">
-        <v>-0.8817310187403369</v>
+        <v>2.67014030684443</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.1012331075083175</v>
+        <v>2.292134216674046</v>
       </c>
     </row>
     <row r="97">
@@ -5766,16 +5766,16 @@
         <v>0.2500260209508095</v>
       </c>
       <c r="N97" t="n">
-        <v>-0.8635681312401856</v>
+        <v>2.485203029801725</v>
       </c>
       <c r="O97" t="n">
-        <v>-0.2603617869792644</v>
+        <v>1.659256120574796</v>
       </c>
       <c r="P97" t="n">
-        <v>-0.2252127276487465</v>
+        <v>1.71196517317242</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.2500260209508095</v>
+        <v>2.222268781272843</v>
       </c>
     </row>
     <row r="98">
@@ -5821,16 +5821,16 @@
         <v>0.1639427134523102</v>
       </c>
       <c r="N98" t="n">
-        <v>-0.6830392900446238</v>
+        <v>2.417771848894063</v>
       </c>
       <c r="O98" t="n">
-        <v>-0.8588914094609181</v>
+        <v>2.787360965537705</v>
       </c>
       <c r="P98" t="n">
-        <v>-0.945794564994352</v>
+        <v>2.653766608824653</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.1639427134523102</v>
+        <v>3.718065315218408</v>
       </c>
     </row>
     <row r="99">
@@ -5876,16 +5876,16 @@
         <v>0.1209755157376785</v>
       </c>
       <c r="N99" t="n">
-        <v>-0.2971814592592834</v>
+        <v>1.326526644607121</v>
       </c>
       <c r="O99" t="n">
-        <v>1.431377026723505</v>
+        <v>5.197580595722489</v>
       </c>
       <c r="P99" t="n">
-        <v>1.462605691629408</v>
+        <v>4.541737706308552</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.1209755157376785</v>
+        <v>2.116719382193002</v>
       </c>
     </row>
     <row r="100">
@@ -5931,16 +5931,16 @@
         <v>-0.1651154266199978</v>
       </c>
       <c r="N100" t="n">
-        <v>-0.2966724848841686</v>
+        <v>1.32514903525943</v>
       </c>
       <c r="O100" t="n">
-        <v>1.218308572597032</v>
+        <v>4.2969502809423</v>
       </c>
       <c r="P100" t="n">
-        <v>1.744115321072271</v>
+        <v>5.279835970259313</v>
       </c>
       <c r="Q100" t="n">
-        <v>-0.1651154266199978</v>
+        <v>1.627967499111516</v>
       </c>
     </row>
     <row r="101">
@@ -5986,16 +5986,16 @@
         <v>0.1099683149016163</v>
       </c>
       <c r="N101" t="n">
-        <v>-0.2966724848841686</v>
+        <v>1.32514903525943</v>
       </c>
       <c r="O101" t="n">
-        <v>1.280979686297509</v>
+        <v>4.734847832172576</v>
       </c>
       <c r="P101" t="n">
-        <v>1.716528390116325</v>
+        <v>5.446975750137996</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.1099683149016163</v>
+        <v>1.822024835205375</v>
       </c>
     </row>
     <row r="102">
@@ -6041,16 +6041,16 @@
         <v>0.08272215197613011</v>
       </c>
       <c r="N102" t="n">
-        <v>-0.2966724848841686</v>
+        <v>1.32514903525943</v>
       </c>
       <c r="O102" t="n">
-        <v>1.274910590446141</v>
+        <v>4.795154670418439</v>
       </c>
       <c r="P102" t="n">
-        <v>1.712121964561651</v>
+        <v>5.435250027111025</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.08272215197613011</v>
+        <v>1.7903179000142</v>
       </c>
     </row>
     <row r="103">
@@ -6096,16 +6096,16 @@
         <v>0.8346008074448787</v>
       </c>
       <c r="N103" t="n">
-        <v>-0.9577631936943858</v>
+        <v>3.904886284646197</v>
       </c>
       <c r="O103" t="n">
-        <v>0.2517419175077739</v>
+        <v>2.449611950443543</v>
       </c>
       <c r="P103" t="n">
-        <v>-0.3239728965234956</v>
+        <v>1.89066367019895</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.8346008074448787</v>
+        <v>3.036693353401258</v>
       </c>
     </row>
     <row r="104">
@@ -6151,16 +6151,16 @@
         <v>1.495207634855213</v>
       </c>
       <c r="N104" t="n">
-        <v>-0.5745530550592962</v>
+        <v>2.498940158055074</v>
       </c>
       <c r="O104" t="n">
-        <v>0.06892301015484002</v>
+        <v>2.79865854519384</v>
       </c>
       <c r="P104" t="n">
-        <v>0.2649283526329083</v>
+        <v>2.937476836859113</v>
       </c>
       <c r="Q104" t="n">
-        <v>1.495207634855213</v>
+        <v>5.174685204436147</v>
       </c>
     </row>
     <row r="105">
@@ -6206,16 +6206,16 @@
         <v>-0.4697221128565625</v>
       </c>
       <c r="N105" t="n">
-        <v>-0.5403225331260108</v>
+        <v>2.376666177155886</v>
       </c>
       <c r="O105" t="n">
-        <v>-0.5260120465329804</v>
+        <v>2.548522481752362</v>
       </c>
       <c r="P105" t="n">
-        <v>-0.9076846531994166</v>
+        <v>3.134766944560493</v>
       </c>
       <c r="Q105" t="n">
-        <v>-0.4697221128565625</v>
+        <v>1.937580798287483</v>
       </c>
     </row>
     <row r="106">
@@ -6261,16 +6261,16 @@
         <v>0.1655137806264552</v>
       </c>
       <c r="N106" t="n">
-        <v>-0.7158183954252227</v>
+        <v>3.49511506342047</v>
       </c>
       <c r="O106" t="n">
-        <v>0.09554580275920387</v>
+        <v>2.140658174060575</v>
       </c>
       <c r="P106" t="n">
-        <v>0.128283877813616</v>
+        <v>2.189256774944597</v>
       </c>
       <c r="Q106" t="n">
-        <v>0.1655137806264552</v>
+        <v>2.916109405343745</v>
       </c>
     </row>
     <row r="107">
@@ -6316,16 +6316,16 @@
         <v>1.252181085373564</v>
       </c>
       <c r="N107" t="n">
-        <v>0.6827391917947425</v>
+        <v>2.999348027006539</v>
       </c>
       <c r="O107" t="n">
-        <v>0.4444324777449168</v>
+        <v>2.671738031402703</v>
       </c>
       <c r="P107" t="n">
-        <v>0.05299040191515324</v>
+        <v>2.652604515322319</v>
       </c>
       <c r="Q107" t="n">
-        <v>1.252181085373564</v>
+        <v>4.522028463102827</v>
       </c>
     </row>
     <row r="108">
@@ -6371,16 +6371,16 @@
         <v>1.089018488587346</v>
       </c>
       <c r="N108" t="n">
-        <v>-0.8448261975625608</v>
+        <v>2.40830611223321</v>
       </c>
       <c r="O108" t="n">
-        <v>0.1945491362402753</v>
+        <v>2.0624391463868</v>
       </c>
       <c r="P108" t="n">
-        <v>-0.1022957484018957</v>
+        <v>1.717681398233026</v>
       </c>
       <c r="Q108" t="n">
-        <v>1.089018488587346</v>
+        <v>4.097937461179494</v>
       </c>
     </row>
     <row r="109">
@@ -6426,16 +6426,16 @@
         <v>0.7558812020842643</v>
       </c>
       <c r="N109" t="n">
-        <v>-1.050854872623524</v>
+        <v>2.863059847740686</v>
       </c>
       <c r="O109" t="n">
-        <v>-0.4666907669503328</v>
+        <v>2.271002250993739</v>
       </c>
       <c r="P109" t="n">
-        <v>0.3392306928908659</v>
+        <v>2.137012457028706</v>
       </c>
       <c r="Q109" t="n">
-        <v>0.7558812020842643</v>
+        <v>2.456229445623936</v>
       </c>
     </row>
     <row r="110">
@@ -6481,16 +6481,16 @@
         <v>0.8536842966993854</v>
       </c>
       <c r="N110" t="n">
-        <v>-1.041972696322271</v>
+        <v>2.849651403363474</v>
       </c>
       <c r="O110" t="n">
-        <v>-0.3556058121991469</v>
+        <v>2.106627776587223</v>
       </c>
       <c r="P110" t="n">
-        <v>0.4822451474606619</v>
+        <v>2.370069459673599</v>
       </c>
       <c r="Q110" t="n">
-        <v>0.8536842966993854</v>
+        <v>2.810337138205083</v>
       </c>
     </row>
     <row r="111">
@@ -6536,16 +6536,16 @@
         <v>0.8627304360410648</v>
       </c>
       <c r="N111" t="n">
-        <v>-1.041187095105499</v>
+        <v>2.848615232694846</v>
       </c>
       <c r="O111" t="n">
-        <v>-0.3738554544186856</v>
+        <v>2.160752607962883</v>
       </c>
       <c r="P111" t="n">
-        <v>0.4316896676428404</v>
+        <v>2.269411246957312</v>
       </c>
       <c r="Q111" t="n">
-        <v>0.8627304360410648</v>
+        <v>2.789534413117943</v>
       </c>
     </row>
     <row r="112">
@@ -6591,16 +6591,16 @@
         <v>0.2835615318236903</v>
       </c>
       <c r="N112" t="n">
-        <v>-0.7017818401716591</v>
+        <v>2.17108557442947</v>
       </c>
       <c r="O112" t="n">
-        <v>0.06897911855927066</v>
+        <v>2.129025915537852</v>
       </c>
       <c r="P112" t="n">
-        <v>0.4960443955267549</v>
+        <v>2.521716529488863</v>
       </c>
       <c r="Q112" t="n">
-        <v>0.2835615318236903</v>
+        <v>1.92852638602754</v>
       </c>
     </row>
     <row r="113">
@@ -6646,16 +6646,16 @@
         <v>0.1669618734975458</v>
       </c>
       <c r="N113" t="n">
-        <v>-0.2907891562667791</v>
+        <v>2.040533897309664</v>
       </c>
       <c r="O113" t="n">
-        <v>-0.1492363429404535</v>
+        <v>2.531650051693248</v>
       </c>
       <c r="P113" t="n">
-        <v>-0.3938344334396867</v>
+        <v>2.517890198451648</v>
       </c>
       <c r="Q113" t="n">
-        <v>0.1669618734975458</v>
+        <v>2.53893572501109</v>
       </c>
     </row>
     <row r="114">
@@ -6701,16 +6701,16 @@
         <v>0.7267150673173398</v>
       </c>
       <c r="N114" t="n">
-        <v>-0.44754350317122</v>
+        <v>2.205417799201014</v>
       </c>
       <c r="O114" t="n">
-        <v>0.5096811717820895</v>
+        <v>1.988606910028442</v>
       </c>
       <c r="P114" t="n">
-        <v>0.5335829979841258</v>
+        <v>2.231146262666779</v>
       </c>
       <c r="Q114" t="n">
-        <v>0.7267150673173398</v>
+        <v>3.396213634744583</v>
       </c>
     </row>
     <row r="115">
@@ -6756,16 +6756,16 @@
         <v>0.1214141759230007</v>
       </c>
       <c r="N115" t="n">
-        <v>-0.9246993432786046</v>
+        <v>2.748515393566803</v>
       </c>
       <c r="O115" t="n">
-        <v>-0.2796014701861182</v>
+        <v>2.33484019567751</v>
       </c>
       <c r="P115" t="n">
-        <v>-0.5248753687983165</v>
+        <v>2.457942407009438</v>
       </c>
       <c r="Q115" t="n">
-        <v>0.1214141759230007</v>
+        <v>1.709271455024197</v>
       </c>
     </row>
     <row r="116">
@@ -6811,16 +6811,16 @@
         <v>0.8444106461406736</v>
       </c>
       <c r="N116" t="n">
-        <v>-0.2820570966614597</v>
+        <v>1.30966426466479</v>
       </c>
       <c r="O116" t="n">
-        <v>0.7485003779999059</v>
+        <v>3.791830589959208</v>
       </c>
       <c r="P116" t="n">
-        <v>0.9369567493205361</v>
+        <v>3.073685826670574</v>
       </c>
       <c r="Q116" t="n">
-        <v>0.8444106461406736</v>
+        <v>3.736789891181963</v>
       </c>
     </row>
     <row r="117">
@@ -6866,16 +6866,16 @@
         <v>-0.04742271645300977</v>
       </c>
       <c r="N117" t="n">
-        <v>-1.285429965735231</v>
+        <v>4.072018973291079</v>
       </c>
       <c r="O117" t="n">
-        <v>1.371561784942553</v>
+        <v>5.223244087182085</v>
       </c>
       <c r="P117" t="n">
-        <v>1.621532652635385</v>
+        <v>6.194806461274899</v>
       </c>
       <c r="Q117" t="n">
-        <v>-0.04742271645300977</v>
+        <v>1.782357157595353</v>
       </c>
     </row>
     <row r="118">
@@ -6921,16 +6921,16 @@
         <v>-1.461342442492448</v>
       </c>
       <c r="N118" t="n">
-        <v>0.3289195027589576</v>
+        <v>2.815116847973004</v>
       </c>
       <c r="O118" t="n">
-        <v>-0.9465913428093041</v>
+        <v>2.538727941913911</v>
       </c>
       <c r="P118" t="n">
-        <v>-0.8730149567470216</v>
+        <v>2.321811435676973</v>
       </c>
       <c r="Q118" t="n">
-        <v>-1.461342442492448</v>
+        <v>4.798308433970981</v>
       </c>
     </row>
     <row r="119">
@@ -6976,16 +6976,16 @@
         <v>-0.3093077423116772</v>
       </c>
       <c r="N119" t="n">
-        <v>-1.324491654842419</v>
+        <v>4.086915521962805</v>
       </c>
       <c r="O119" t="n">
-        <v>1.263960570937192</v>
+        <v>4.858901815096546</v>
       </c>
       <c r="P119" t="n">
-        <v>1.627601783199441</v>
+        <v>6.171881869390368</v>
       </c>
       <c r="Q119" t="n">
-        <v>-0.3093077423116772</v>
+        <v>2.015731327611276</v>
       </c>
     </row>
     <row r="120">
@@ -7031,16 +7031,16 @@
         <v>0.9916071937405938</v>
       </c>
       <c r="N120" t="n">
-        <v>0.3782091376070999</v>
+        <v>3.349928529970989</v>
       </c>
       <c r="O120" t="n">
-        <v>0.079008170401335</v>
+        <v>2.379157695155043</v>
       </c>
       <c r="P120" t="n">
-        <v>0.2305401381867446</v>
+        <v>2.138343178669034</v>
       </c>
       <c r="Q120" t="n">
-        <v>0.9916071937405938</v>
+        <v>2.837211220582237</v>
       </c>
     </row>
     <row r="121">
@@ -7086,16 +7086,16 @@
         <v>0.5863714820995871</v>
       </c>
       <c r="N121" t="n">
-        <v>-0.270753922064327</v>
+        <v>1.303066804296908</v>
       </c>
       <c r="O121" t="n">
-        <v>1.316390583554881</v>
+        <v>5.175153298443432</v>
       </c>
       <c r="P121" t="n">
-        <v>1.364246875831147</v>
+        <v>4.061515820067465</v>
       </c>
       <c r="Q121" t="n">
-        <v>0.5863714820995871</v>
+        <v>2.50840194108477</v>
       </c>
     </row>
     <row r="122">
@@ -7141,16 +7141,16 @@
         <v>0.2790424841075904</v>
       </c>
       <c r="N122" t="n">
-        <v>-0.2703278330132661</v>
+        <v>1.301902323255968</v>
       </c>
       <c r="O122" t="n">
-        <v>0.7885230953063085</v>
+        <v>3.565674290682603</v>
       </c>
       <c r="P122" t="n">
-        <v>1.496919695771622</v>
+        <v>4.346321886092113</v>
       </c>
       <c r="Q122" t="n">
-        <v>0.2790424841075904</v>
+        <v>1.737109575734281</v>
       </c>
     </row>
     <row r="123">
@@ -7196,16 +7196,16 @@
         <v>0.3118578266169834</v>
       </c>
       <c r="N123" t="n">
-        <v>-0.2703278330132661</v>
+        <v>1.301902323255968</v>
       </c>
       <c r="O123" t="n">
-        <v>1.044930154874264</v>
+        <v>4.209298692371386</v>
       </c>
       <c r="P123" t="n">
-        <v>1.496988941757144</v>
+        <v>4.445795274541799</v>
       </c>
       <c r="Q123" t="n">
-        <v>0.3118578266169834</v>
+        <v>1.749283615551316</v>
       </c>
     </row>
     <row r="124">
@@ -7251,16 +7251,16 @@
         <v>1.347718195202683</v>
       </c>
       <c r="N124" t="n">
-        <v>-0.130828844439088</v>
+        <v>2.715129936992698</v>
       </c>
       <c r="O124" t="n">
-        <v>1.262142151791918</v>
+        <v>4.253458617069012</v>
       </c>
       <c r="P124" t="n">
-        <v>1.842409014403078</v>
+        <v>6.372269910884174</v>
       </c>
       <c r="Q124" t="n">
-        <v>1.347718195202683</v>
+        <v>5.291226250235574</v>
       </c>
     </row>
     <row r="125">
@@ -7306,16 +7306,16 @@
         <v>0.08741987843057428</v>
       </c>
       <c r="N125" t="n">
-        <v>-0.7224238501370177</v>
+        <v>2.697482664254247</v>
       </c>
       <c r="O125" t="n">
-        <v>0.5752308305225579</v>
+        <v>2.040019264282771</v>
       </c>
       <c r="P125" t="n">
-        <v>0.201387582390462</v>
+        <v>1.791772875638604</v>
       </c>
       <c r="Q125" t="n">
-        <v>0.08741987843057428</v>
+        <v>2.931891301869815</v>
       </c>
     </row>
     <row r="126">
@@ -7361,16 +7361,16 @@
         <v>1.341886038959776</v>
       </c>
       <c r="N126" t="n">
-        <v>-0.06081639689934414</v>
+        <v>2.921598267101229</v>
       </c>
       <c r="O126" t="n">
-        <v>1.418953006397953</v>
+        <v>4.927833557352307</v>
       </c>
       <c r="P126" t="n">
-        <v>1.917917436325733</v>
+        <v>6.642090071848855</v>
       </c>
       <c r="Q126" t="n">
-        <v>1.341886038959776</v>
+        <v>5.199186343760307</v>
       </c>
     </row>
     <row r="127">
@@ -7416,16 +7416,16 @@
         <v>-0.1186884205611648</v>
       </c>
       <c r="N127" t="n">
-        <v>-0.6809321049321132</v>
+        <v>2.222969320905805</v>
       </c>
       <c r="O127" t="n">
-        <v>0.4902957118234466</v>
+        <v>2.619907619932116</v>
       </c>
       <c r="P127" t="n">
-        <v>0.7026463969162925</v>
+        <v>2.690113787112671</v>
       </c>
       <c r="Q127" t="n">
-        <v>-0.1186884205611648</v>
+        <v>2.574331710922056</v>
       </c>
     </row>
     <row r="128">
@@ -7471,16 +7471,16 @@
         <v>0.342045775537838</v>
       </c>
       <c r="N128" t="n">
-        <v>0.3048523846138911</v>
+        <v>1.973653793692838</v>
       </c>
       <c r="O128" t="n">
-        <v>-0.1953308115880916</v>
+        <v>2.763826275828518</v>
       </c>
       <c r="P128" t="n">
-        <v>-0.443658866496723</v>
+        <v>2.488098419143232</v>
       </c>
       <c r="Q128" t="n">
-        <v>0.342045775537838</v>
+        <v>1.786489729411345</v>
       </c>
     </row>
     <row r="129">
@@ -7526,16 +7526,16 @@
         <v>1.793033307230061</v>
       </c>
       <c r="N129" t="n">
-        <v>-0.7624381328494221</v>
+        <v>2.255228071365575</v>
       </c>
       <c r="O129" t="n">
-        <v>0.7133148912230149</v>
+        <v>2.956107226218931</v>
       </c>
       <c r="P129" t="n">
-        <v>0.2082023637751252</v>
+        <v>1.958531734924205</v>
       </c>
       <c r="Q129" t="n">
-        <v>1.793033307230061</v>
+        <v>6.406067906474937</v>
       </c>
     </row>
     <row r="130">
@@ -7581,16 +7581,16 @@
         <v>1.735290112135911</v>
       </c>
       <c r="N130" t="n">
-        <v>-0.7606430392285033</v>
+        <v>2.25308063362591</v>
       </c>
       <c r="O130" t="n">
-        <v>0.4523600042939637</v>
+        <v>2.515439722311018</v>
       </c>
       <c r="P130" t="n">
-        <v>0.006259918908703026</v>
+        <v>1.834745568508274</v>
       </c>
       <c r="Q130" t="n">
-        <v>1.735290112135911</v>
+        <v>6.196354573962226</v>
       </c>
     </row>
     <row r="131">
@@ -7636,16 +7636,16 @@
         <v>0.4013885138845585</v>
       </c>
       <c r="N131" t="n">
-        <v>-0.5147387983249586</v>
+        <v>2.697960198238746</v>
       </c>
       <c r="O131" t="n">
-        <v>0.1354544604012734</v>
+        <v>2.256366955578931</v>
       </c>
       <c r="P131" t="n">
-        <v>-0.1466293553620616</v>
+        <v>2.546754027659559</v>
       </c>
       <c r="Q131" t="n">
-        <v>0.4013885138845585</v>
+        <v>2.143202268889013</v>
       </c>
     </row>
     <row r="132">
@@ -7691,16 +7691,16 @@
         <v>0.7723788684748408</v>
       </c>
       <c r="N132" t="n">
-        <v>0.5895661508121477</v>
+        <v>3.815530006073176</v>
       </c>
       <c r="O132" t="n">
-        <v>-0.2279447656209576</v>
+        <v>2.278218331044251</v>
       </c>
       <c r="P132" t="n">
-        <v>-0.6166958423248653</v>
+        <v>2.11882314805241</v>
       </c>
       <c r="Q132" t="n">
-        <v>0.7723788684748408</v>
+        <v>2.112230760174583</v>
       </c>
     </row>
     <row r="133">
@@ -7746,16 +7746,16 @@
         <v>0.5406393112510154</v>
       </c>
       <c r="N133" t="n">
-        <v>-0.5033738471328473</v>
+        <v>1.880565447656661</v>
       </c>
       <c r="O133" t="n">
-        <v>0.3002449086329222</v>
+        <v>2.602351469922296</v>
       </c>
       <c r="P133" t="n">
-        <v>0.7316310684362</v>
+        <v>3.424826328172435</v>
       </c>
       <c r="Q133" t="n">
-        <v>0.5406393112510154</v>
+        <v>2.526150707027098</v>
       </c>
     </row>
     <row r="134">
@@ -7801,16 +7801,16 @@
         <v>0.5207481434004753</v>
       </c>
       <c r="N134" t="n">
-        <v>-0.9000669527611405</v>
+        <v>2.591957907533508</v>
       </c>
       <c r="O134" t="n">
-        <v>0.8517410335509608</v>
+        <v>3.479109950880065</v>
       </c>
       <c r="P134" t="n">
-        <v>0.7279368806746416</v>
+        <v>2.718285486594087</v>
       </c>
       <c r="Q134" t="n">
-        <v>0.5207481434004753</v>
+        <v>2.443817492637832</v>
       </c>
     </row>
     <row r="135">
@@ -7856,16 +7856,16 @@
         <v>0.6713653414874239</v>
       </c>
       <c r="N135" t="n">
-        <v>-0.9045952038538135</v>
+        <v>2.604819428444906</v>
       </c>
       <c r="O135" t="n">
-        <v>0.6292005243950116</v>
+        <v>3.07911216959669</v>
       </c>
       <c r="P135" t="n">
-        <v>0.6480723128851376</v>
+        <v>2.481580405418331</v>
       </c>
       <c r="Q135" t="n">
-        <v>0.6713653414874239</v>
+        <v>3.0938615844834</v>
       </c>
     </row>
     <row r="136">
@@ -7911,16 +7911,16 @@
         <v>0.2247757142567061</v>
       </c>
       <c r="N136" t="n">
-        <v>-0.1441181949606221</v>
+        <v>1.875313970097393</v>
       </c>
       <c r="O136" t="n">
-        <v>0.2505758091280109</v>
+        <v>3.000380279784801</v>
       </c>
       <c r="P136" t="n">
-        <v>0.4772044454595886</v>
+        <v>2.705968174891865</v>
       </c>
       <c r="Q136" t="n">
-        <v>0.2247757142567061</v>
+        <v>2.851589620783881</v>
       </c>
     </row>
     <row r="137">
@@ -7966,16 +7966,16 @@
         <v>0.6889957584785188</v>
       </c>
       <c r="N137" t="n">
-        <v>-0.9362127224416693</v>
+        <v>2.586536084270581</v>
       </c>
       <c r="O137" t="n">
-        <v>0.6329712232273209</v>
+        <v>2.687369567907075</v>
       </c>
       <c r="P137" t="n">
-        <v>1.387193686780724</v>
+        <v>5.174564247051864</v>
       </c>
       <c r="Q137" t="n">
-        <v>0.6889957584785188</v>
+        <v>2.445415059014396</v>
       </c>
     </row>
     <row r="138">
@@ -8021,16 +8021,16 @@
         <v>0.693828147931704</v>
       </c>
       <c r="N138" t="n">
-        <v>-0.9360373450071131</v>
+        <v>2.587411347753803</v>
       </c>
       <c r="O138" t="n">
-        <v>0.5859149379068793</v>
+        <v>2.593661138327104</v>
       </c>
       <c r="P138" t="n">
-        <v>1.346626015830972</v>
+        <v>5.060404365468832</v>
       </c>
       <c r="Q138" t="n">
-        <v>0.693828147931704</v>
+        <v>2.352403882811407</v>
       </c>
     </row>
     <row r="139">
@@ -8076,16 +8076,16 @@
         <v>0.7684215306134023</v>
       </c>
       <c r="N139" t="n">
-        <v>-0.9360373450071131</v>
+        <v>2.587411347753803</v>
       </c>
       <c r="O139" t="n">
-        <v>0.3741309575170869</v>
+        <v>2.272916217340596</v>
       </c>
       <c r="P139" t="n">
-        <v>1.281953869880988</v>
+        <v>4.900113653503583</v>
       </c>
       <c r="Q139" t="n">
-        <v>0.7684215306134023</v>
+        <v>2.584652635363046</v>
       </c>
     </row>
     <row r="140">
@@ -8131,16 +8131,16 @@
         <v>0.9727566011812183</v>
       </c>
       <c r="N140" t="n">
-        <v>-0.9307314768482893</v>
+        <v>2.577724809341278</v>
       </c>
       <c r="O140" t="n">
-        <v>0.5966733882422365</v>
+        <v>2.943084977525879</v>
       </c>
       <c r="P140" t="n">
-        <v>1.669743166768373</v>
+        <v>6.039448358091303</v>
       </c>
       <c r="Q140" t="n">
-        <v>0.9727566011812183</v>
+        <v>3.882010648303505</v>
       </c>
     </row>
     <row r="141">
@@ -8186,16 +8186,16 @@
         <v>0.7776352348177802</v>
       </c>
       <c r="N141" t="n">
-        <v>0.1170265004975752</v>
+        <v>1.923090631473577</v>
       </c>
       <c r="O141" t="n">
-        <v>0.04705242105631758</v>
+        <v>2.070615384372667</v>
       </c>
       <c r="P141" t="n">
-        <v>1.070722352381209</v>
+        <v>4.070274113311873</v>
       </c>
       <c r="Q141" t="n">
-        <v>0.7776352348177802</v>
+        <v>2.551415428532546</v>
       </c>
     </row>
     <row r="142">
@@ -8241,16 +8241,16 @@
         <v>-0.2252331969530622</v>
       </c>
       <c r="N142" t="n">
-        <v>0.04482685471408741</v>
+        <v>1.321291871507815</v>
       </c>
       <c r="O142" t="n">
-        <v>0.0560416380664339</v>
+        <v>1.450437043105026</v>
       </c>
       <c r="P142" t="n">
-        <v>0.1556547447129411</v>
+        <v>1.529034536998673</v>
       </c>
       <c r="Q142" t="n">
-        <v>-0.2252331969530622</v>
+        <v>1.195317169453938</v>
       </c>
     </row>
     <row r="143">
@@ -8296,16 +8296,16 @@
         <v>0.2293658241622279</v>
       </c>
       <c r="N143" t="n">
-        <v>-0.5823581242606722</v>
+        <v>1.910777054334874</v>
       </c>
       <c r="O143" t="n">
-        <v>-0.6322315796851544</v>
+        <v>2.3040510663321</v>
       </c>
       <c r="P143" t="n">
-        <v>-0.5609003192737004</v>
+        <v>2.178148752605484</v>
       </c>
       <c r="Q143" t="n">
-        <v>0.2293658241622279</v>
+        <v>1.627429928247719</v>
       </c>
     </row>
     <row r="144">
@@ -8351,16 +8351,16 @@
         <v>0.01967829983210607</v>
       </c>
       <c r="N144" t="n">
-        <v>0.7678035848120539</v>
+        <v>2.173786992242729</v>
       </c>
       <c r="O144" t="n">
-        <v>-0.1089288261043097</v>
+        <v>2.804749972318763</v>
       </c>
       <c r="P144" t="n">
-        <v>0.2668502683301044</v>
+        <v>2.84021192016925</v>
       </c>
       <c r="Q144" t="n">
-        <v>0.01967829983210607</v>
+        <v>1.555324079687063</v>
       </c>
     </row>
     <row r="145">
@@ -8406,16 +8406,16 @@
         <v>0.3676906440988436</v>
       </c>
       <c r="N145" t="n">
-        <v>-0.5703871503546533</v>
+        <v>2.178105883257676</v>
       </c>
       <c r="O145" t="n">
-        <v>0.09982504581511648</v>
+        <v>2.166220257454123</v>
       </c>
       <c r="P145" t="n">
-        <v>0.4146367166439524</v>
+        <v>2.75593739291797</v>
       </c>
       <c r="Q145" t="n">
-        <v>0.3676906440988436</v>
+        <v>2.454371071728152</v>
       </c>
     </row>
     <row r="146">
@@ -8461,16 +8461,16 @@
         <v>1.05122849774653</v>
       </c>
       <c r="N146" t="n">
-        <v>-1.737477369164066</v>
+        <v>5.902237588078711</v>
       </c>
       <c r="O146" t="n">
-        <v>1.591771565652147</v>
+        <v>5.415894461751251</v>
       </c>
       <c r="P146" t="n">
-        <v>2.422366386931322</v>
+        <v>8.455664599057043</v>
       </c>
       <c r="Q146" t="n">
-        <v>1.05122849774653</v>
+        <v>2.676836254631571</v>
       </c>
     </row>
     <row r="147">
@@ -8516,16 +8516,16 @@
         <v>0.4786834999371939</v>
       </c>
       <c r="N147" t="n">
-        <v>-0.4211806131705595</v>
+        <v>1.608247248740148</v>
       </c>
       <c r="O147" t="n">
-        <v>-0.4341657776859555</v>
+        <v>2.15794719033162</v>
       </c>
       <c r="P147" t="n">
-        <v>-0.4216603077233746</v>
+        <v>1.966272808872225</v>
       </c>
       <c r="Q147" t="n">
-        <v>0.4786834999371939</v>
+        <v>2.490845741398899</v>
       </c>
     </row>
     <row r="148">
@@ -8571,16 +8571,16 @@
         <v>0.2375345130517153</v>
       </c>
       <c r="N148" t="n">
-        <v>0.9933252362337399</v>
+        <v>3.276295974807267</v>
       </c>
       <c r="O148" t="n">
-        <v>0.4044980652461015</v>
+        <v>2.718314628064847</v>
       </c>
       <c r="P148" t="n">
-        <v>-0.008708850253496292</v>
+        <v>2.647018477557575</v>
       </c>
       <c r="Q148" t="n">
-        <v>0.2375345130517153</v>
+        <v>2.453578890829972</v>
       </c>
     </row>
     <row r="149">
@@ -8626,16 +8626,16 @@
         <v>-0.6901037710086617</v>
       </c>
       <c r="N149" t="n">
-        <v>-0.4333896813857858</v>
+        <v>2.515075321274804</v>
       </c>
       <c r="O149" t="n">
-        <v>-0.567797024992227</v>
+        <v>2.062498127601813</v>
       </c>
       <c r="P149" t="n">
-        <v>-0.2268184497128612</v>
+        <v>2.293366009557585</v>
       </c>
       <c r="Q149" t="n">
-        <v>-0.6901037710086617</v>
+        <v>3.046486809757335</v>
       </c>
     </row>
     <row r="150">
@@ -8681,16 +8681,16 @@
         <v>-0.4570551461847187</v>
       </c>
       <c r="N150" t="n">
-        <v>-0.9440301342116727</v>
+        <v>2.70675243049747</v>
       </c>
       <c r="O150" t="n">
-        <v>0.8307553545371688</v>
+        <v>3.110938105182473</v>
       </c>
       <c r="P150" t="n">
-        <v>0.688790545122835</v>
+        <v>2.573211050062977</v>
       </c>
       <c r="Q150" t="n">
-        <v>-0.4570551461847187</v>
+        <v>3.14437576435901</v>
       </c>
     </row>
     <row r="151">
@@ -8736,16 +8736,16 @@
         <v>1.403903625971358</v>
       </c>
       <c r="N151" t="n">
-        <v>-0.09215196564968287</v>
+        <v>2.21765048073904</v>
       </c>
       <c r="O151" t="n">
-        <v>0.7689810751097195</v>
+        <v>3.115368669611034</v>
       </c>
       <c r="P151" t="n">
-        <v>0.8968545291071592</v>
+        <v>3.490261880750237</v>
       </c>
       <c r="Q151" t="n">
-        <v>1.403903625971358</v>
+        <v>5.182202207501306</v>
       </c>
     </row>
     <row r="152">
@@ -8791,16 +8791,16 @@
         <v>0.9501327540149692</v>
       </c>
       <c r="N152" t="n">
-        <v>-0.07137418598194217</v>
+        <v>2.231753907341595</v>
       </c>
       <c r="O152" t="n">
-        <v>1.00377855330764</v>
+        <v>3.721724316450925</v>
       </c>
       <c r="P152" t="n">
-        <v>0.9521186769019854</v>
+        <v>3.585222379285208</v>
       </c>
       <c r="Q152" t="n">
-        <v>0.9501327540149692</v>
+        <v>3.516119799671872</v>
       </c>
     </row>
     <row r="153">
@@ -8846,16 +8846,16 @@
         <v>1.235509836916256</v>
       </c>
       <c r="N153" t="n">
-        <v>-0.2018445387972912</v>
+        <v>2.62671483283592</v>
       </c>
       <c r="O153" t="n">
-        <v>1.176685027458265</v>
+        <v>3.618766224787427</v>
       </c>
       <c r="P153" t="n">
-        <v>1.312919102301165</v>
+        <v>4.637015340697197</v>
       </c>
       <c r="Q153" t="n">
-        <v>1.235509836916256</v>
+        <v>4.572443467182844</v>
       </c>
     </row>
     <row r="154">
@@ -8901,16 +8901,16 @@
         <v>0.9204302046139943</v>
       </c>
       <c r="N154" t="n">
-        <v>-1.528741786663286</v>
+        <v>5.066024605506481</v>
       </c>
       <c r="O154" t="n">
-        <v>1.176121456243855</v>
+        <v>4.459580260594996</v>
       </c>
       <c r="P154" t="n">
-        <v>2.138377527710563</v>
+        <v>7.514559566610571</v>
       </c>
       <c r="Q154" t="n">
-        <v>0.9204302046139943</v>
+        <v>3.192813575538102</v>
       </c>
     </row>
     <row r="155">
@@ -8956,16 +8956,16 @@
         <v>1.541514503042495</v>
       </c>
       <c r="N155" t="n">
-        <v>0.5072628361739648</v>
+        <v>2.310223436919313</v>
       </c>
       <c r="O155" t="n">
-        <v>0.7152534795301202</v>
+        <v>2.94511888596332</v>
       </c>
       <c r="P155" t="n">
-        <v>0.3260432198157479</v>
+        <v>1.909560098770489</v>
       </c>
       <c r="Q155" t="n">
-        <v>1.541514503042495</v>
+        <v>5.032506214301981</v>
       </c>
     </row>
     <row r="156">
@@ -9011,16 +9011,16 @@
         <v>-0.7276310385425361</v>
       </c>
       <c r="N156" t="n">
-        <v>0.6845049986083328</v>
+        <v>2.771692955301992</v>
       </c>
       <c r="O156" t="n">
-        <v>0.3786551449683247</v>
+        <v>2.097836050727382</v>
       </c>
       <c r="P156" t="n">
-        <v>0.04290361466791613</v>
+        <v>1.703375788329789</v>
       </c>
       <c r="Q156" t="n">
-        <v>-0.7276310385425361</v>
+        <v>3.409138503707707</v>
       </c>
     </row>
     <row r="157">
@@ -9066,16 +9066,16 @@
         <v>-0.3046255469205625</v>
       </c>
       <c r="N157" t="n">
-        <v>0.6845049986083328</v>
+        <v>2.771692955301992</v>
       </c>
       <c r="O157" t="n">
-        <v>0.5460916629888525</v>
+        <v>2.635071719381701</v>
       </c>
       <c r="P157" t="n">
-        <v>0.0428012486426738</v>
+        <v>1.696388831190256</v>
       </c>
       <c r="Q157" t="n">
-        <v>-0.3046255469205625</v>
+        <v>3.530688047746802</v>
       </c>
     </row>
     <row r="158">
@@ -9121,16 +9121,16 @@
         <v>-0.7884704866091357</v>
       </c>
       <c r="N158" t="n">
-        <v>0.6845049986083328</v>
+        <v>2.771692955301992</v>
       </c>
       <c r="O158" t="n">
-        <v>0.3830925992302572</v>
+        <v>2.130385224660003</v>
       </c>
       <c r="P158" t="n">
-        <v>0.03918061470721755</v>
+        <v>1.70673523183391</v>
       </c>
       <c r="Q158" t="n">
-        <v>-0.7884704866091357</v>
+        <v>3.532042617556892</v>
       </c>
     </row>
     <row r="159">
@@ -9176,16 +9176,16 @@
         <v>0.01305639470153434</v>
       </c>
       <c r="N159" t="n">
-        <v>0.6845049986083328</v>
+        <v>2.771692955301992</v>
       </c>
       <c r="O159" t="n">
-        <v>0.5890776808599771</v>
+        <v>2.59515564534929</v>
       </c>
       <c r="P159" t="n">
-        <v>0.01086549800006157</v>
+        <v>1.705416546947501</v>
       </c>
       <c r="Q159" t="n">
-        <v>0.01305639470153434</v>
+        <v>2.973377843018261</v>
       </c>
     </row>
     <row r="160">
@@ -9231,16 +9231,16 @@
         <v>1.524622649611249</v>
       </c>
       <c r="N160" t="n">
-        <v>0.388836258364619</v>
+        <v>2.028534688896023</v>
       </c>
       <c r="O160" t="n">
-        <v>0.68120134701888</v>
+        <v>2.730235969058488</v>
       </c>
       <c r="P160" t="n">
-        <v>0.3921644385476712</v>
+        <v>2.252847118780726</v>
       </c>
       <c r="Q160" t="n">
-        <v>1.524622649611249</v>
+        <v>4.904967629330263</v>
       </c>
     </row>
     <row r="161">
@@ -9286,16 +9286,16 @@
         <v>1.405130934814708</v>
       </c>
       <c r="N161" t="n">
-        <v>-0.7383806402019377</v>
+        <v>2.784906945292382</v>
       </c>
       <c r="O161" t="n">
-        <v>0.586472938410571</v>
+        <v>2.480349064958512</v>
       </c>
       <c r="P161" t="n">
-        <v>0.6352414640040476</v>
+        <v>2.640038355780322</v>
       </c>
       <c r="Q161" t="n">
-        <v>1.405130934814708</v>
+        <v>5.006027360783797</v>
       </c>
     </row>
     <row r="162">
@@ -9341,16 +9341,16 @@
         <v>1.425037347616403</v>
       </c>
       <c r="N162" t="n">
-        <v>-0.7253554020802256</v>
+        <v>2.725779015135443</v>
       </c>
       <c r="O162" t="n">
-        <v>0.6810265304894284</v>
+        <v>2.682793337882012</v>
       </c>
       <c r="P162" t="n">
-        <v>0.6862159673882288</v>
+        <v>2.729115348787794</v>
       </c>
       <c r="Q162" t="n">
-        <v>1.425037347616403</v>
+        <v>5.161736852425105</v>
       </c>
     </row>
     <row r="163">
@@ -9396,16 +9396,16 @@
         <v>0.5634110889868932</v>
       </c>
       <c r="N163" t="n">
-        <v>-0.2732824957534387</v>
+        <v>2.110902351668474</v>
       </c>
       <c r="O163" t="n">
-        <v>-0.2433177867176367</v>
+        <v>1.951343303472119</v>
       </c>
       <c r="P163" t="n">
-        <v>0.07728163685516813</v>
+        <v>1.667627206865027</v>
       </c>
       <c r="Q163" t="n">
-        <v>0.5634110889868932</v>
+        <v>2.04681108468902</v>
       </c>
     </row>
     <row r="164">
@@ -9451,16 +9451,16 @@
         <v>1.922337311977765</v>
       </c>
       <c r="N164" t="n">
-        <v>1.935912691903029</v>
+        <v>6.737476411446833</v>
       </c>
       <c r="O164" t="n">
-        <v>-0.2844798176264349</v>
+        <v>2.584152194252618</v>
       </c>
       <c r="P164" t="n">
-        <v>0.7064315796279608</v>
+        <v>2.919839371416417</v>
       </c>
       <c r="Q164" t="n">
-        <v>1.922337311977765</v>
+        <v>6.302327146372688</v>
       </c>
     </row>
     <row r="165">
@@ -9506,16 +9506,16 @@
         <v>1.910245814638452</v>
       </c>
       <c r="N165" t="n">
-        <v>1.930576179592439</v>
+        <v>6.719965353479462</v>
       </c>
       <c r="O165" t="n">
-        <v>-0.424861908844966</v>
+        <v>2.357054161500452</v>
       </c>
       <c r="P165" t="n">
-        <v>0.6614877464995185</v>
+        <v>2.913896793804883</v>
       </c>
       <c r="Q165" t="n">
-        <v>1.910245814638452</v>
+        <v>6.488059803770253</v>
       </c>
     </row>
     <row r="166">
@@ -9561,16 +9561,16 @@
         <v>1.884404213416207</v>
       </c>
       <c r="N166" t="n">
-        <v>1.930576179592439</v>
+        <v>6.719965353479462</v>
       </c>
       <c r="O166" t="n">
-        <v>-0.3057903270738314</v>
+        <v>2.404865634808239</v>
       </c>
       <c r="P166" t="n">
-        <v>0.7411131897113362</v>
+        <v>2.972457535039625</v>
       </c>
       <c r="Q166" t="n">
-        <v>1.884404213416207</v>
+        <v>6.333808469965868</v>
       </c>
     </row>
     <row r="167">
@@ -9616,16 +9616,16 @@
         <v>-0.06195856124976062</v>
       </c>
       <c r="N167" t="n">
-        <v>-0.4326145115621006</v>
+        <v>2.0333296429461</v>
       </c>
       <c r="O167" t="n">
-        <v>0.4164194682759765</v>
+        <v>2.483725738951379</v>
       </c>
       <c r="P167" t="n">
-        <v>-0.189992522420779</v>
+        <v>1.486485043825651</v>
       </c>
       <c r="Q167" t="n">
-        <v>-0.06195856124976062</v>
+        <v>1.786535060536565</v>
       </c>
     </row>
     <row r="168">
@@ -9671,16 +9671,16 @@
         <v>0.05728313246632432</v>
       </c>
       <c r="N168" t="n">
-        <v>-1.204794190039022</v>
+        <v>4.052869059640315</v>
       </c>
       <c r="O168" t="n">
-        <v>0.08513014689011884</v>
+        <v>1.94104196193656</v>
       </c>
       <c r="P168" t="n">
-        <v>0.2960087321555563</v>
+        <v>2.432303751639863</v>
       </c>
       <c r="Q168" t="n">
-        <v>0.05728313246632432</v>
+        <v>2.188698865188787</v>
       </c>
     </row>
     <row r="169">
@@ -9726,16 +9726,16 @@
         <v>1.78420858242101</v>
       </c>
       <c r="N169" t="n">
-        <v>-0.6816586067306758</v>
+        <v>2.096134710960277</v>
       </c>
       <c r="O169" t="n">
-        <v>0.680090143451944</v>
+        <v>2.459462549452713</v>
       </c>
       <c r="P169" t="n">
-        <v>0.7290316571272335</v>
+        <v>2.476562086502601</v>
       </c>
       <c r="Q169" t="n">
-        <v>1.78420858242101</v>
+        <v>6.185629006816897</v>
       </c>
     </row>
     <row r="170">
@@ -9781,16 +9781,16 @@
         <v>1.855795230692376</v>
       </c>
       <c r="N170" t="n">
-        <v>-0.677760199058669</v>
+        <v>2.090000508075909</v>
       </c>
       <c r="O170" t="n">
-        <v>0.6337754177851626</v>
+        <v>2.393534884807764</v>
       </c>
       <c r="P170" t="n">
-        <v>0.6908241995502552</v>
+        <v>2.444154714221361</v>
       </c>
       <c r="Q170" t="n">
-        <v>1.855795230692376</v>
+        <v>6.468722337049702</v>
       </c>
     </row>
     <row r="171">
@@ -9836,16 +9836,16 @@
         <v>1.53957402136522</v>
       </c>
       <c r="N171" t="n">
-        <v>-0.4689711830675899</v>
+        <v>1.914562212580009</v>
       </c>
       <c r="O171" t="n">
-        <v>0.5910272974343166</v>
+        <v>2.217138287946336</v>
       </c>
       <c r="P171" t="n">
-        <v>0.6091642062978797</v>
+        <v>2.428265332786684</v>
       </c>
       <c r="Q171" t="n">
-        <v>1.53957402136522</v>
+        <v>5.728448006039657</v>
       </c>
     </row>
     <row r="172">
@@ -9891,16 +9891,16 @@
         <v>-0.4632450777190198</v>
       </c>
       <c r="N172" t="n">
-        <v>-0.08617598948202364</v>
+        <v>2.194873677242501</v>
       </c>
       <c r="O172" t="n">
-        <v>0.543741236792318</v>
+        <v>2.670519952427983</v>
       </c>
       <c r="P172" t="n">
-        <v>0.4554648134996503</v>
+        <v>2.50162123771503</v>
       </c>
       <c r="Q172" t="n">
-        <v>-0.4632450777190198</v>
+        <v>2.553937637670192</v>
       </c>
     </row>
     <row r="173">
@@ -9946,16 +9946,16 @@
         <v>1.908978114219493</v>
       </c>
       <c r="N173" t="n">
-        <v>-0.7465748859923096</v>
+        <v>2.17780994635802</v>
       </c>
       <c r="O173" t="n">
-        <v>0.5958131868030565</v>
+        <v>2.254156467591794</v>
       </c>
       <c r="P173" t="n">
-        <v>0.6767050715800962</v>
+        <v>2.370468238892217</v>
       </c>
       <c r="Q173" t="n">
-        <v>1.908978114219493</v>
+        <v>6.578780191389206</v>
       </c>
     </row>
     <row r="174">
@@ -10001,16 +10001,16 @@
         <v>-0.2039889327628653</v>
       </c>
       <c r="N174" t="n">
-        <v>-0.311616209708324</v>
+        <v>1.3018398048183</v>
       </c>
       <c r="O174" t="n">
-        <v>-0.164423103000179</v>
+        <v>1.621782518785447</v>
       </c>
       <c r="P174" t="n">
-        <v>0.390610351875551</v>
+        <v>2.52847743996669</v>
       </c>
       <c r="Q174" t="n">
-        <v>-0.2039889327628653</v>
+        <v>2.059397506986832</v>
       </c>
     </row>
     <row r="175">
@@ -10056,16 +10056,16 @@
         <v>-0.2320725915177718</v>
       </c>
       <c r="N175" t="n">
-        <v>-0.4784108997160336</v>
+        <v>2.618304775993302</v>
       </c>
       <c r="O175" t="n">
-        <v>0.2774043070595779</v>
+        <v>2.051468728281519</v>
       </c>
       <c r="P175" t="n">
-        <v>0.2074622092271067</v>
+        <v>1.718819240681665</v>
       </c>
       <c r="Q175" t="n">
-        <v>-0.2320725915177718</v>
+        <v>1.997179292560504</v>
       </c>
     </row>
     <row r="176">
@@ -10111,16 +10111,16 @@
         <v>-0.4252492613227154</v>
       </c>
       <c r="N176" t="n">
-        <v>-0.2976835904682803</v>
+        <v>1.295897522464227</v>
       </c>
       <c r="O176" t="n">
-        <v>-0.03108744917649683</v>
+        <v>1.641308873355514</v>
       </c>
       <c r="P176" t="n">
-        <v>0.05371493388959843</v>
+        <v>1.937242850281987</v>
       </c>
       <c r="Q176" t="n">
-        <v>-0.4252492613227154</v>
+        <v>2.567532308864059</v>
       </c>
     </row>
     <row r="177">
@@ -10166,16 +10166,16 @@
         <v>-0.3573126848389774</v>
       </c>
       <c r="N177" t="n">
-        <v>-0.2970514764237743</v>
+        <v>1.296561114090987</v>
       </c>
       <c r="O177" t="n">
-        <v>-0.1834334314323569</v>
+        <v>1.705084134468351</v>
       </c>
       <c r="P177" t="n">
-        <v>-0.008816202552124739</v>
+        <v>1.847072748552115</v>
       </c>
       <c r="Q177" t="n">
-        <v>-0.3573126848389774</v>
+        <v>2.860337380936377</v>
       </c>
     </row>
     <row r="178">
@@ -10221,16 +10221,16 @@
         <v>0.6792598918729125</v>
       </c>
       <c r="N178" t="n">
-        <v>-0.9966557130753708</v>
+        <v>2.7531704762996</v>
       </c>
       <c r="O178" t="n">
-        <v>-0.1912787875979391</v>
+        <v>2.365345414144172</v>
       </c>
       <c r="P178" t="n">
-        <v>-0.1251215455589406</v>
+        <v>2.008563082359489</v>
       </c>
       <c r="Q178" t="n">
-        <v>0.6792598918729125</v>
+        <v>2.614709799060469</v>
       </c>
     </row>
     <row r="179">
@@ -10276,16 +10276,16 @@
         <v>0.0910848930713937</v>
       </c>
       <c r="N179" t="n">
-        <v>-0.4466174335748936</v>
+        <v>1.48690738154835</v>
       </c>
       <c r="O179" t="n">
-        <v>0.312598227134581</v>
+        <v>1.649630070598016</v>
       </c>
       <c r="P179" t="n">
-        <v>0.3932053944697866</v>
+        <v>1.667839137909873</v>
       </c>
       <c r="Q179" t="n">
-        <v>0.0910848930713937</v>
+        <v>3.386238762372853</v>
       </c>
     </row>
     <row r="180">
@@ -10331,16 +10331,16 @@
         <v>0.4485892383654662</v>
       </c>
       <c r="N180" t="n">
-        <v>0.1564797649192675</v>
+        <v>2.323936242480435</v>
       </c>
       <c r="O180" t="n">
-        <v>-0.2856112316940346</v>
+        <v>2.680581653670595</v>
       </c>
       <c r="P180" t="n">
-        <v>-0.534795608016549</v>
+        <v>2.513745388720132</v>
       </c>
       <c r="Q180" t="n">
-        <v>0.4485892383654662</v>
+        <v>1.880663390016087</v>
       </c>
     </row>
     <row r="181">
@@ -10386,16 +10386,16 @@
         <v>0.7401801966073993</v>
       </c>
       <c r="N181" t="n">
-        <v>0.4207676955801314</v>
+        <v>1.990661114551651</v>
       </c>
       <c r="O181" t="n">
-        <v>0.2170642928715221</v>
+        <v>2.905227715355155</v>
       </c>
       <c r="P181" t="n">
-        <v>-0.400613262476133</v>
+        <v>2.418635846100037</v>
       </c>
       <c r="Q181" t="n">
-        <v>0.7401801966073993</v>
+        <v>2.435274436932562</v>
       </c>
     </row>
     <row r="182">
@@ -10441,16 +10441,16 @@
         <v>0.1624665503962459</v>
       </c>
       <c r="N182" t="n">
-        <v>0.5654421192130283</v>
+        <v>2.37392470772607</v>
       </c>
       <c r="O182" t="n">
-        <v>0.1218749435151254</v>
+        <v>1.945063604056511</v>
       </c>
       <c r="P182" t="n">
-        <v>0.525827140316155</v>
+        <v>2.724149394293534</v>
       </c>
       <c r="Q182" t="n">
-        <v>0.1624665503962459</v>
+        <v>1.723083735818826</v>
       </c>
     </row>
     <row r="183">
@@ -10496,16 +10496,16 @@
         <v>0.6699676305738289</v>
       </c>
       <c r="N183" t="n">
-        <v>0.5670390691559813</v>
+        <v>2.377631534519933</v>
       </c>
       <c r="O183" t="n">
-        <v>-0.0998307255919339</v>
+        <v>1.914711582421529</v>
       </c>
       <c r="P183" t="n">
-        <v>0.5332842548155016</v>
+        <v>2.85095400673292</v>
       </c>
       <c r="Q183" t="n">
-        <v>0.6699676305738289</v>
+        <v>2.762209462356351</v>
       </c>
     </row>
     <row r="184">
@@ -10551,16 +10551,16 @@
         <v>0.05804924924892672</v>
       </c>
       <c r="N184" t="n">
-        <v>-0.4452399533837541</v>
+        <v>1.46317420759535</v>
       </c>
       <c r="O184" t="n">
-        <v>0.5219891114606716</v>
+        <v>1.946757602990669</v>
       </c>
       <c r="P184" t="n">
-        <v>0.3718002849811172</v>
+        <v>1.704785251992742</v>
       </c>
       <c r="Q184" t="n">
-        <v>0.05804924924892672</v>
+        <v>2.496251790709909</v>
       </c>
     </row>
     <row r="185">
@@ -10606,16 +10606,16 @@
         <v>0.7073289241063168</v>
       </c>
       <c r="N185" t="n">
-        <v>0.2050677808522462</v>
+        <v>1.825656324540944</v>
       </c>
       <c r="O185" t="n">
-        <v>-0.1699776792743843</v>
+        <v>1.7815300914992</v>
       </c>
       <c r="P185" t="n">
-        <v>0.4658317401567356</v>
+        <v>2.262444562290771</v>
       </c>
       <c r="Q185" t="n">
-        <v>0.7073289241063168</v>
+        <v>2.148771438734975</v>
       </c>
     </row>
     <row r="186">
@@ -10661,16 +10661,16 @@
         <v>2.034380025820208</v>
       </c>
       <c r="N186" t="n">
-        <v>0.97725455671713</v>
+        <v>2.540408057048623</v>
       </c>
       <c r="O186" t="n">
-        <v>0.6287357634931172</v>
+        <v>2.85898369762462</v>
       </c>
       <c r="P186" t="n">
-        <v>0.6260473333525993</v>
+        <v>3.140902745791611</v>
       </c>
       <c r="Q186" t="n">
-        <v>2.034380025820208</v>
+        <v>7.09419603908067</v>
       </c>
     </row>
     <row r="187">
@@ -10716,16 +10716,16 @@
         <v>0.4506081601385172</v>
       </c>
       <c r="N187" t="n">
-        <v>-0.6391923392430445</v>
+        <v>2.078245608389528</v>
       </c>
       <c r="O187" t="n">
-        <v>-0.9823590706136637</v>
+        <v>3.244084620516067</v>
       </c>
       <c r="P187" t="n">
-        <v>0.01512174831631258</v>
+        <v>1.680299919085545</v>
       </c>
       <c r="Q187" t="n">
-        <v>0.4506081601385172</v>
+        <v>2.489638055404366</v>
       </c>
     </row>
     <row r="188">
@@ -10771,16 +10771,16 @@
         <v>-1.043799475502469</v>
       </c>
       <c r="N188" t="n">
-        <v>-0.8967034666783599</v>
+        <v>2.520826753951756</v>
       </c>
       <c r="O188" t="n">
-        <v>-0.6836883021827859</v>
+        <v>2.895105534835551</v>
       </c>
       <c r="P188" t="n">
-        <v>-0.6764110700117572</v>
+        <v>3.351400683515469</v>
       </c>
       <c r="Q188" t="n">
-        <v>-1.043799475502469</v>
+        <v>4.716950141984831</v>
       </c>
     </row>
     <row r="189">
@@ -10826,16 +10826,16 @@
         <v>-0.9336137796869393</v>
       </c>
       <c r="N189" t="n">
-        <v>-0.6416202350919709</v>
+        <v>2.049654015843315</v>
       </c>
       <c r="O189" t="n">
-        <v>-0.5731908749487603</v>
+        <v>2.76783175594181</v>
       </c>
       <c r="P189" t="n">
-        <v>-0.549297807541605</v>
+        <v>3.162322283167833</v>
       </c>
       <c r="Q189" t="n">
-        <v>-0.9336137796869393</v>
+        <v>4.374495003536577</v>
       </c>
     </row>
     <row r="190">
@@ -10881,16 +10881,16 @@
         <v>1.411533450689324</v>
       </c>
       <c r="N190" t="n">
-        <v>-0.3036371638385302</v>
+        <v>1.861442373270004</v>
       </c>
       <c r="O190" t="n">
-        <v>0.09280212972146924</v>
+        <v>2.917418157801754</v>
       </c>
       <c r="P190" t="n">
-        <v>-0.2472154693081126</v>
+        <v>2.106990142210189</v>
       </c>
       <c r="Q190" t="n">
-        <v>1.411533450689324</v>
+        <v>4.241523019039875</v>
       </c>
     </row>
     <row r="191">
@@ -10936,16 +10936,16 @@
         <v>-0.854080694575062</v>
       </c>
       <c r="N191" t="n">
-        <v>-0.643579480538108</v>
+        <v>2.06059009435315</v>
       </c>
       <c r="O191" t="n">
-        <v>-0.6992094759593873</v>
+        <v>2.854778360663479</v>
       </c>
       <c r="P191" t="n">
-        <v>-0.8209766079805088</v>
+        <v>3.281725103605965</v>
       </c>
       <c r="Q191" t="n">
-        <v>-0.854080694575062</v>
+        <v>4.493284225245431</v>
       </c>
     </row>
     <row r="192">
@@ -10991,16 +10991,16 @@
         <v>1.807566552534341</v>
       </c>
       <c r="N192" t="n">
-        <v>1.076103760833486</v>
+        <v>2.613944299891544</v>
       </c>
       <c r="O192" t="n">
-        <v>0.6533357296263432</v>
+        <v>2.81442661049752</v>
       </c>
       <c r="P192" t="n">
-        <v>0.5320851189329829</v>
+        <v>2.882025020388402</v>
       </c>
       <c r="Q192" t="n">
-        <v>1.807566552534341</v>
+        <v>6.016837129453622</v>
       </c>
     </row>
     <row r="193">
@@ -11046,16 +11046,16 @@
         <v>0.7697270103895119</v>
       </c>
       <c r="N193" t="n">
-        <v>0.2597121935308851</v>
+        <v>2.412998814508378</v>
       </c>
       <c r="O193" t="n">
-        <v>0.1149349123079847</v>
+        <v>2.216709127764278</v>
       </c>
       <c r="P193" t="n">
-        <v>-0.5209470539604352</v>
+        <v>2.113071602133541</v>
       </c>
       <c r="Q193" t="n">
-        <v>0.7697270103895119</v>
+        <v>2.395973287762445</v>
       </c>
     </row>
     <row r="194">
@@ -11101,16 +11101,16 @@
         <v>0.05818529905219341</v>
       </c>
       <c r="N194" t="n">
-        <v>-0.3319427088748958</v>
+        <v>1.770323055848824</v>
       </c>
       <c r="O194" t="n">
-        <v>1.113629873157133</v>
+        <v>4.300634951943874</v>
       </c>
       <c r="P194" t="n">
-        <v>1.602625019869305</v>
+        <v>5.730603755395323</v>
       </c>
       <c r="Q194" t="n">
-        <v>0.05818529905219341</v>
+        <v>2.066397654019722</v>
       </c>
     </row>
     <row r="195">
@@ -11156,16 +11156,16 @@
         <v>0.1974746176224037</v>
       </c>
       <c r="N195" t="n">
-        <v>-0.340137994559564</v>
+        <v>1.766958800205393</v>
       </c>
       <c r="O195" t="n">
-        <v>1.080059131488807</v>
+        <v>4.066033205275265</v>
       </c>
       <c r="P195" t="n">
-        <v>1.617311325454711</v>
+        <v>5.753439240089818</v>
       </c>
       <c r="Q195" t="n">
-        <v>0.1974746176224037</v>
+        <v>1.935410472244647</v>
       </c>
     </row>
     <row r="196">
@@ -11211,16 +11211,16 @@
         <v>0.1777476721458298</v>
       </c>
       <c r="N196" t="n">
-        <v>-0.340137994559564</v>
+        <v>1.766958800205393</v>
       </c>
       <c r="O196" t="n">
-        <v>0.9332230928431522</v>
+        <v>4.036489286325447</v>
       </c>
       <c r="P196" t="n">
-        <v>1.525087675995648</v>
+        <v>5.542908541130596</v>
       </c>
       <c r="Q196" t="n">
-        <v>0.1777476721458298</v>
+        <v>2.29475144434945</v>
       </c>
     </row>
     <row r="197">
@@ -11266,16 +11266,16 @@
         <v>0.06970880738430808</v>
       </c>
       <c r="N197" t="n">
-        <v>-0.340137994559564</v>
+        <v>1.766958800205393</v>
       </c>
       <c r="O197" t="n">
-        <v>1.00687790858717</v>
+        <v>4.123783835590561</v>
       </c>
       <c r="P197" t="n">
-        <v>1.563427136859056</v>
+        <v>5.625387206149487</v>
       </c>
       <c r="Q197" t="n">
-        <v>0.06970880738430808</v>
+        <v>2.269996710083683</v>
       </c>
     </row>
     <row r="198">
@@ -11321,16 +11321,16 @@
         <v>2.521062138514758</v>
       </c>
       <c r="N198" t="n">
-        <v>-1.372465160986138</v>
+        <v>3.567332892591335</v>
       </c>
       <c r="O198" t="n">
-        <v>0.09298188384726776</v>
+        <v>1.857884362761083</v>
       </c>
       <c r="P198" t="n">
-        <v>0.2466211222215488</v>
+        <v>1.497130499344381</v>
       </c>
       <c r="Q198" t="n">
-        <v>2.521062138514758</v>
+        <v>8.721905814895949</v>
       </c>
     </row>
     <row r="199">
@@ -11376,16 +11376,16 @@
         <v>-0.1905140613948214</v>
       </c>
       <c r="N199" t="n">
-        <v>-0.9344794678811944</v>
+        <v>3.920876969304526</v>
       </c>
       <c r="O199" t="n">
-        <v>1.085260926688883</v>
+        <v>3.50190188705584</v>
       </c>
       <c r="P199" t="n">
-        <v>1.805572374741464</v>
+        <v>5.934243243064021</v>
       </c>
       <c r="Q199" t="n">
-        <v>-0.1905140613948214</v>
+        <v>3.030664819962269</v>
       </c>
     </row>
     <row r="200">
@@ -11431,16 +11431,16 @@
         <v>-0.2640087755333976</v>
       </c>
       <c r="N200" t="n">
-        <v>-0.1649187633231321</v>
+        <v>1.910753942187014</v>
       </c>
       <c r="O200" t="n">
-        <v>0.3383770106974741</v>
+        <v>2.328936275355102</v>
       </c>
       <c r="P200" t="n">
-        <v>0.5553310476727341</v>
+        <v>2.667020454188754</v>
       </c>
       <c r="Q200" t="n">
-        <v>-0.2640087755333976</v>
+        <v>3.013625706161997</v>
       </c>
     </row>
     <row r="201">
@@ -11486,16 +11486,16 @@
         <v>1.513578865270267</v>
       </c>
       <c r="N201" t="n">
-        <v>-0.4629436580443111</v>
+        <v>1.841174817282964</v>
       </c>
       <c r="O201" t="n">
-        <v>0.2853444141488514</v>
+        <v>2.286134383300312</v>
       </c>
       <c r="P201" t="n">
-        <v>0.3754612909449689</v>
+        <v>2.046316171154843</v>
       </c>
       <c r="Q201" t="n">
-        <v>1.513578865270267</v>
+        <v>5.224371152548003</v>
       </c>
     </row>
     <row r="202">
@@ -11541,16 +11541,16 @@
         <v>0.3637138331160262</v>
       </c>
       <c r="N202" t="n">
-        <v>-0.4789728953136466</v>
+        <v>1.961963179744154</v>
       </c>
       <c r="O202" t="n">
-        <v>-0.3289290730632906</v>
+        <v>2.683094339448017</v>
       </c>
       <c r="P202" t="n">
-        <v>0.8162984620578059</v>
+        <v>2.213337984902454</v>
       </c>
       <c r="Q202" t="n">
-        <v>0.3637138331160262</v>
+        <v>2.164821524926671</v>
       </c>
     </row>
     <row r="203">
@@ -11596,16 +11596,16 @@
         <v>0.555763325131254</v>
       </c>
       <c r="N203" t="n">
-        <v>-0.4855636733493153</v>
+        <v>2.043208476814029</v>
       </c>
       <c r="O203" t="n">
-        <v>-0.4512050200824034</v>
+        <v>2.777734136151245</v>
       </c>
       <c r="P203" t="n">
-        <v>0.7887134142013004</v>
+        <v>2.101316001496357</v>
       </c>
       <c r="Q203" t="n">
-        <v>0.555763325131254</v>
+        <v>2.451517766962783</v>
       </c>
     </row>
     <row r="204">
@@ -11651,16 +11651,16 @@
         <v>1.087267868587904</v>
       </c>
       <c r="N204" t="n">
-        <v>-2.190341216753824</v>
+        <v>7.459130730029432</v>
       </c>
       <c r="O204" t="n">
-        <v>1.81182850608557</v>
+        <v>6.006259686389974</v>
       </c>
       <c r="P204" t="n">
-        <v>2.441693100698605</v>
+        <v>8.45684187926439</v>
       </c>
       <c r="Q204" t="n">
-        <v>1.087267868587904</v>
+        <v>4.240426084840457</v>
       </c>
     </row>
     <row r="205">
@@ -11706,16 +11706,16 @@
         <v>-0.4472441034779757</v>
       </c>
       <c r="N205" t="n">
-        <v>-0.4360264575799946</v>
+        <v>1.665233528518803</v>
       </c>
       <c r="O205" t="n">
-        <v>0.3884873551919137</v>
+        <v>1.742119411996382</v>
       </c>
       <c r="P205" t="n">
-        <v>0.1339787264515226</v>
+        <v>1.524431975431149</v>
       </c>
       <c r="Q205" t="n">
-        <v>-0.4472441034779757</v>
+        <v>2.563935262973191</v>
       </c>
     </row>
     <row r="206">
@@ -11761,16 +11761,16 @@
         <v>0.7731363601744117</v>
       </c>
       <c r="N206" t="n">
-        <v>-0.6385492573111183</v>
+        <v>2.428989557990058</v>
       </c>
       <c r="O206" t="n">
-        <v>-0.03321005656714344</v>
+        <v>2.97557391740812</v>
       </c>
       <c r="P206" t="n">
-        <v>0.5263345903761159</v>
+        <v>1.817475217384704</v>
       </c>
       <c r="Q206" t="n">
-        <v>0.7731363601744117</v>
+        <v>2.834006160266742</v>
       </c>
     </row>
     <row r="207">
@@ -11816,16 +11816,16 @@
         <v>0.5821779540036244</v>
       </c>
       <c r="N207" t="n">
-        <v>-0.6652916080736579</v>
+        <v>2.48902005018221</v>
       </c>
       <c r="O207" t="n">
-        <v>0.1561064614862952</v>
+        <v>3.186204309190619</v>
       </c>
       <c r="P207" t="n">
-        <v>0.5499498614430923</v>
+        <v>1.955381602777167</v>
       </c>
       <c r="Q207" t="n">
-        <v>0.5821779540036244</v>
+        <v>2.37819378919412</v>
       </c>
     </row>
     <row r="208">
@@ -11871,16 +11871,16 @@
         <v>0.2206854344418447</v>
       </c>
       <c r="N208" t="n">
-        <v>-0.8572994858563838</v>
+        <v>3.128044759458884</v>
       </c>
       <c r="O208" t="n">
-        <v>-0.5299445296785171</v>
+        <v>2.830584365182581</v>
       </c>
       <c r="P208" t="n">
-        <v>-0.2792060343494017</v>
+        <v>2.816540020726264</v>
       </c>
       <c r="Q208" t="n">
-        <v>0.2206854344418447</v>
+        <v>1.717043873183651</v>
       </c>
     </row>
     <row r="209">
@@ -11926,16 +11926,16 @@
         <v>0.3508615969745749</v>
       </c>
       <c r="N209" t="n">
-        <v>-0.856586167306306</v>
+        <v>3.136007934502032</v>
       </c>
       <c r="O209" t="n">
-        <v>-0.3647010586005117</v>
+        <v>2.625645146139614</v>
       </c>
       <c r="P209" t="n">
-        <v>-0.261103469198794</v>
+        <v>2.563774415145427</v>
       </c>
       <c r="Q209" t="n">
-        <v>0.3508615969745749</v>
+        <v>1.827787906620635</v>
       </c>
     </row>
     <row r="210">
@@ -11981,16 +11981,16 @@
         <v>0.7499207493259046</v>
       </c>
       <c r="N210" t="n">
-        <v>-1.510175390586686</v>
+        <v>4.873942823177492</v>
       </c>
       <c r="O210" t="n">
-        <v>0.0288400978178119</v>
+        <v>2.294623416441341</v>
       </c>
       <c r="P210" t="n">
-        <v>0.5938020459165821</v>
+        <v>3.015952691112883</v>
       </c>
       <c r="Q210" t="n">
-        <v>0.7499207493259046</v>
+        <v>2.858277005058936</v>
       </c>
     </row>
     <row r="211">
@@ -12036,16 +12036,16 @@
         <v>0.4862565071471893</v>
       </c>
       <c r="N211" t="n">
-        <v>-0.0283333915451372</v>
+        <v>1.19769427057583</v>
       </c>
       <c r="O211" t="n">
-        <v>0.3686650810140115</v>
+        <v>2.093185755179964</v>
       </c>
       <c r="P211" t="n">
-        <v>0.8745533246095285</v>
+        <v>2.816995968705835</v>
       </c>
       <c r="Q211" t="n">
-        <v>0.4862565071471893</v>
+        <v>2.316308210158887</v>
       </c>
     </row>
     <row r="212">
@@ -12091,16 +12091,16 @@
         <v>0.3411987984368918</v>
       </c>
       <c r="N212" t="n">
-        <v>-0.0283333915451372</v>
+        <v>1.19769427057583</v>
       </c>
       <c r="O212" t="n">
-        <v>0.3927108234543839</v>
+        <v>2.204426717079749</v>
       </c>
       <c r="P212" t="n">
-        <v>0.9038272287479415</v>
+        <v>2.88519680336896</v>
       </c>
       <c r="Q212" t="n">
-        <v>0.3411987984368918</v>
+        <v>2.055376748202256</v>
       </c>
     </row>
     <row r="213">
@@ -12146,16 +12146,16 @@
         <v>0.9957201182720186</v>
       </c>
       <c r="N213" t="n">
-        <v>-1.455303062228988</v>
+        <v>4.732049181190817</v>
       </c>
       <c r="O213" t="n">
-        <v>0.7187586608570187</v>
+        <v>2.745807396063241</v>
       </c>
       <c r="P213" t="n">
-        <v>1.573199461520495</v>
+        <v>5.16915212543516</v>
       </c>
       <c r="Q213" t="n">
-        <v>0.9957201182720186</v>
+        <v>2.891217279608373</v>
       </c>
     </row>
     <row r="214">
@@ -12201,16 +12201,16 @@
         <v>0.9775991204514412</v>
       </c>
       <c r="N214" t="n">
-        <v>-0.493234966296429</v>
+        <v>2.287436779944312</v>
       </c>
       <c r="O214" t="n">
-        <v>0.7850102744129372</v>
+        <v>2.530838608152325</v>
       </c>
       <c r="P214" t="n">
-        <v>0.5961349169266307</v>
+        <v>2.137337497797112</v>
       </c>
       <c r="Q214" t="n">
-        <v>0.9775991204514412</v>
+        <v>4.999442949572887</v>
       </c>
     </row>
     <row r="215">
@@ -12256,16 +12256,16 @@
         <v>0.9373676876575113</v>
       </c>
       <c r="N215" t="n">
-        <v>0.4723190888331889</v>
+        <v>4.02905364071803</v>
       </c>
       <c r="O215" t="n">
-        <v>0.7874533119294029</v>
+        <v>2.506296660385972</v>
       </c>
       <c r="P215" t="n">
-        <v>0.4981688616141717</v>
+        <v>2.693639569794891</v>
       </c>
       <c r="Q215" t="n">
-        <v>0.9373676876575113</v>
+        <v>2.864061827942751</v>
       </c>
     </row>
     <row r="216">
@@ -12311,16 +12311,16 @@
         <v>0.501621892036628</v>
       </c>
       <c r="N216" t="n">
-        <v>-1.091164558567053</v>
+        <v>3.01970254584063</v>
       </c>
       <c r="O216" t="n">
-        <v>0.3631159089293595</v>
+        <v>3.123973843519556</v>
       </c>
       <c r="P216" t="n">
-        <v>1.118570847871613</v>
+        <v>4.803087120235999</v>
       </c>
       <c r="Q216" t="n">
-        <v>0.501621892036628</v>
+        <v>3.135959588215837</v>
       </c>
     </row>
     <row r="217">
@@ -12366,16 +12366,16 @@
         <v>0.5923426687982956</v>
       </c>
       <c r="N217" t="n">
-        <v>-1.088836738568144</v>
+        <v>3.014301070792015</v>
       </c>
       <c r="O217" t="n">
-        <v>0.3285696994427716</v>
+        <v>3.009014198809978</v>
       </c>
       <c r="P217" t="n">
-        <v>1.081474162987292</v>
+        <v>4.700377788076653</v>
       </c>
       <c r="Q217" t="n">
-        <v>0.5923426687982956</v>
+        <v>3.226143925126307</v>
       </c>
     </row>
     <row r="218">
@@ -12421,16 +12421,16 @@
         <v>0.6936773654120892</v>
       </c>
       <c r="N218" t="n">
-        <v>-0.8759160598919915</v>
+        <v>2.757368289118329</v>
       </c>
       <c r="O218" t="n">
-        <v>0.5299345761356981</v>
+        <v>2.466916233198551</v>
       </c>
       <c r="P218" t="n">
-        <v>0.600454523001079</v>
+        <v>2.65820748881256</v>
       </c>
       <c r="Q218" t="n">
-        <v>0.6936773654120892</v>
+        <v>2.702100902258019</v>
       </c>
     </row>
     <row r="219">
@@ -12476,16 +12476,16 @@
         <v>-0.7136061272516786</v>
       </c>
       <c r="N219" t="n">
-        <v>-0.6899951812563301</v>
+        <v>2.192489427799946</v>
       </c>
       <c r="O219" t="n">
-        <v>0.6887599731491664</v>
+        <v>2.868587682021426</v>
       </c>
       <c r="P219" t="n">
-        <v>0.4979668973051417</v>
+        <v>2.386004834409267</v>
       </c>
       <c r="Q219" t="n">
-        <v>-0.7136061272516786</v>
+        <v>3.087780841372055</v>
       </c>
     </row>
     <row r="220">
@@ -12531,16 +12531,16 @@
         <v>0.9142491501581116</v>
       </c>
       <c r="N220" t="n">
-        <v>0.3350087700016625</v>
+        <v>1.547728128321037</v>
       </c>
       <c r="O220" t="n">
-        <v>1.865819273847707</v>
+        <v>6.308364635540326</v>
       </c>
       <c r="P220" t="n">
-        <v>0.6045879642668949</v>
+        <v>1.905042077584703</v>
       </c>
       <c r="Q220" t="n">
-        <v>0.9142491501581116</v>
+        <v>2.50226363036504</v>
       </c>
     </row>
     <row r="221">
@@ -12586,16 +12586,16 @@
         <v>0.9748188855749594</v>
       </c>
       <c r="N221" t="n">
-        <v>0.3350087700016625</v>
+        <v>1.547728128321037</v>
       </c>
       <c r="O221" t="n">
-        <v>1.554679997176871</v>
+        <v>4.972848986642508</v>
       </c>
       <c r="P221" t="n">
-        <v>0.5631678431770937</v>
+        <v>1.840244769306229</v>
       </c>
       <c r="Q221" t="n">
-        <v>0.9748188855749594</v>
+        <v>2.665423096024082</v>
       </c>
     </row>
     <row r="222">
@@ -12641,16 +12641,16 @@
         <v>-0.9428755733371418</v>
       </c>
       <c r="N222" t="n">
-        <v>0.6336038350370976</v>
+        <v>2.300425188360387</v>
       </c>
       <c r="O222" t="n">
-        <v>-1.057984937684857</v>
+        <v>2.853970963194905</v>
       </c>
       <c r="P222" t="n">
-        <v>-0.7005758666263955</v>
+        <v>2.537817326805158</v>
       </c>
       <c r="Q222" t="n">
-        <v>-0.9428755733371418</v>
+        <v>4.984014241362597</v>
       </c>
     </row>
     <row r="223">
@@ -12696,16 +12696,16 @@
         <v>-0.9360162019499066</v>
       </c>
       <c r="N223" t="n">
-        <v>0.6336038350370976</v>
+        <v>2.300425188360387</v>
       </c>
       <c r="O223" t="n">
-        <v>-1.032725932299729</v>
+        <v>2.776928265638849</v>
       </c>
       <c r="P223" t="n">
-        <v>-0.7572094927252918</v>
+        <v>2.582969685754938</v>
       </c>
       <c r="Q223" t="n">
-        <v>-0.9360162019499066</v>
+        <v>4.708917761606594</v>
       </c>
     </row>
     <row r="224">
@@ -12751,16 +12751,16 @@
         <v>1.278238566189312</v>
       </c>
       <c r="N224" t="n">
-        <v>-0.8113356392924277</v>
+        <v>2.676540031930819</v>
       </c>
       <c r="O224" t="n">
-        <v>0.3787765136812583</v>
+        <v>2.061210967866428</v>
       </c>
       <c r="P224" t="n">
-        <v>0.2202723237345207</v>
+        <v>3.236267563011093</v>
       </c>
       <c r="Q224" t="n">
-        <v>1.278238566189312</v>
+        <v>4.602594852752628</v>
       </c>
     </row>
     <row r="225">
@@ -12806,16 +12806,16 @@
         <v>-0.392172523595381</v>
       </c>
       <c r="N225" t="n">
-        <v>-1.035841359459404</v>
+        <v>2.610559023465165</v>
       </c>
       <c r="O225" t="n">
-        <v>0.1091504106158717</v>
+        <v>1.672188072189433</v>
       </c>
       <c r="P225" t="n">
-        <v>0.3987731549218154</v>
+        <v>1.908385313371336</v>
       </c>
       <c r="Q225" t="n">
-        <v>-0.392172523595381</v>
+        <v>2.240059211227251</v>
       </c>
     </row>
     <row r="226">
@@ -12861,16 +12861,16 @@
         <v>1.184322576048826</v>
       </c>
       <c r="N226" t="n">
-        <v>-0.7543025037522588</v>
+        <v>2.389905268234507</v>
       </c>
       <c r="O226" t="n">
-        <v>2.666220788734535</v>
+        <v>9.241931062323848</v>
       </c>
       <c r="P226" t="n">
-        <v>2.854130055589076</v>
+        <v>9.968329786278922</v>
       </c>
       <c r="Q226" t="n">
-        <v>1.184322576048826</v>
+        <v>4.493309575177236</v>
       </c>
     </row>
     <row r="227">
@@ -12916,16 +12916,16 @@
         <v>1.154865174838856</v>
       </c>
       <c r="N227" t="n">
-        <v>-0.7437952601506354</v>
+        <v>2.40735131398186</v>
       </c>
       <c r="O227" t="n">
-        <v>2.65871516673974</v>
+        <v>9.209552559411659</v>
       </c>
       <c r="P227" t="n">
-        <v>2.85423591934483</v>
+        <v>9.968927615684839</v>
       </c>
       <c r="Q227" t="n">
-        <v>1.154865174838856</v>
+        <v>4.410669572083036</v>
       </c>
     </row>
     <row r="228">
@@ -12971,16 +12971,16 @@
         <v>0.5551774965817797</v>
       </c>
       <c r="N228" t="n">
-        <v>1.211960800014237</v>
+        <v>3.195210681814029</v>
       </c>
       <c r="O228" t="n">
-        <v>-0.1017286226917381</v>
+        <v>2.338231773945643</v>
       </c>
       <c r="P228" t="n">
-        <v>-0.157179771273553</v>
+        <v>2.009662538357819</v>
       </c>
       <c r="Q228" t="n">
-        <v>0.5551774965817797</v>
+        <v>2.998766780727124</v>
       </c>
     </row>
     <row r="229">
@@ -13026,16 +13026,16 @@
         <v>2.101238577606251</v>
       </c>
       <c r="N229" t="n">
-        <v>-0.3305305865757032</v>
+        <v>1.660607968646761</v>
       </c>
       <c r="O229" t="n">
-        <v>0.8706300279976619</v>
+        <v>4.023599526605364</v>
       </c>
       <c r="P229" t="n">
-        <v>0.5829959119934978</v>
+        <v>2.368644992020365</v>
       </c>
       <c r="Q229" t="n">
-        <v>2.101238577606251</v>
+        <v>7.099738414598983</v>
       </c>
     </row>
     <row r="230">
@@ -13081,16 +13081,16 @@
         <v>0.7691058527671459</v>
       </c>
       <c r="N230" t="n">
-        <v>-1.195282660624509</v>
+        <v>4.224175735711043</v>
       </c>
       <c r="O230" t="n">
-        <v>0.08500352940742778</v>
+        <v>3.737051779389442</v>
       </c>
       <c r="P230" t="n">
-        <v>1.10084630620972</v>
+        <v>4.369397348641815</v>
       </c>
       <c r="Q230" t="n">
-        <v>0.7691058527671459</v>
+        <v>2.563463288883245</v>
       </c>
     </row>
     <row r="231">
@@ -13136,16 +13136,16 @@
         <v>0.2411377065165974</v>
       </c>
       <c r="N231" t="n">
-        <v>-1.02793135830075</v>
+        <v>2.8984485759527</v>
       </c>
       <c r="O231" t="n">
-        <v>1.013095493619808</v>
+        <v>2.507494028838473</v>
       </c>
       <c r="P231" t="n">
-        <v>1.30869802194745</v>
+        <v>3.80829836025966</v>
       </c>
       <c r="Q231" t="n">
-        <v>0.2411377065165974</v>
+        <v>2.184418263148199</v>
       </c>
     </row>
     <row r="232">
@@ -13191,16 +13191,16 @@
         <v>0.4639379183605027</v>
       </c>
       <c r="N232" t="n">
-        <v>-1.024703273784781</v>
+        <v>2.895081031120851</v>
       </c>
       <c r="O232" t="n">
-        <v>0.8948379765528628</v>
+        <v>2.232836841110288</v>
       </c>
       <c r="P232" t="n">
-        <v>1.260536175155351</v>
+        <v>3.588263416177987</v>
       </c>
       <c r="Q232" t="n">
-        <v>0.4639379183605027</v>
+        <v>2.149588622351437</v>
       </c>
     </row>
     <row r="233">
@@ -13246,16 +13246,16 @@
         <v>0.2999522091632691</v>
       </c>
       <c r="N233" t="n">
-        <v>-0.7779094878220206</v>
+        <v>2.598484456780314</v>
       </c>
       <c r="O233" t="n">
-        <v>0.7655845728710766</v>
+        <v>2.815746792914056</v>
       </c>
       <c r="P233" t="n">
-        <v>0.8725338298900652</v>
+        <v>3.888426820562861</v>
       </c>
       <c r="Q233" t="n">
-        <v>0.2999522091632691</v>
+        <v>1.722327704714912</v>
       </c>
     </row>
     <row r="234">
@@ -13301,16 +13301,16 @@
         <v>-0.414855755523972</v>
       </c>
       <c r="N234" t="n">
-        <v>-0.8286458515473597</v>
+        <v>2.184207312215384</v>
       </c>
       <c r="O234" t="n">
-        <v>0.6614860619415399</v>
+        <v>2.322065328863493</v>
       </c>
       <c r="P234" t="n">
-        <v>0.7668849970419517</v>
+        <v>2.76971333996979</v>
       </c>
       <c r="Q234" t="n">
-        <v>-0.414855755523972</v>
+        <v>2.255316136432633</v>
       </c>
     </row>
     <row r="235">
@@ -13356,16 +13356,16 @@
         <v>0.1266211342486392</v>
       </c>
       <c r="N235" t="n">
-        <v>-0.5922992308195029</v>
+        <v>2.008286740519936</v>
       </c>
       <c r="O235" t="n">
-        <v>1.417471524817142</v>
+        <v>4.112989325640598</v>
       </c>
       <c r="P235" t="n">
-        <v>0.7956071610443722</v>
+        <v>2.551196942801114</v>
       </c>
       <c r="Q235" t="n">
-        <v>0.1266211342486392</v>
+        <v>1.483656704045578</v>
       </c>
     </row>
     <row r="236">
@@ -13411,16 +13411,16 @@
         <v>0.1340661659093932</v>
       </c>
       <c r="N236" t="n">
-        <v>-0.5922992308195029</v>
+        <v>2.008286740519936</v>
       </c>
       <c r="O236" t="n">
-        <v>1.344068488513773</v>
+        <v>3.899605348172581</v>
       </c>
       <c r="P236" t="n">
-        <v>0.5545683679706455</v>
+        <v>2.090513713707055</v>
       </c>
       <c r="Q236" t="n">
-        <v>0.1340661659093932</v>
+        <v>1.464751399209001</v>
       </c>
     </row>
     <row r="237">
@@ -13466,16 +13466,16 @@
         <v>0.2309146028276651</v>
       </c>
       <c r="N237" t="n">
-        <v>-1.026847095653442</v>
+        <v>2.829973839809157</v>
       </c>
       <c r="O237" t="n">
-        <v>1.017212219877824</v>
+        <v>2.535384531132481</v>
       </c>
       <c r="P237" t="n">
-        <v>1.30718958814611</v>
+        <v>3.823435422616106</v>
       </c>
       <c r="Q237" t="n">
-        <v>0.2309146028276651</v>
+        <v>2.069781211372589</v>
       </c>
     </row>
     <row r="238">
@@ -13521,16 +13521,16 @@
         <v>0.847317075275109</v>
       </c>
       <c r="N238" t="n">
-        <v>-0.5960089210188027</v>
+        <v>1.910392137771025</v>
       </c>
       <c r="O238" t="n">
-        <v>1.393968330816686</v>
+        <v>4.30605756502556</v>
       </c>
       <c r="P238" t="n">
-        <v>1.001808483443393</v>
+        <v>2.670078035474258</v>
       </c>
       <c r="Q238" t="n">
-        <v>0.847317075275109</v>
+        <v>3.101359887275777</v>
       </c>
     </row>
     <row r="239">
@@ -13576,16 +13576,16 @@
         <v>0.4361177456485267</v>
       </c>
       <c r="N239" t="n">
-        <v>-0.7087280533364669</v>
+        <v>2.022539237375831</v>
       </c>
       <c r="O239" t="n">
-        <v>0.3184272747455495</v>
+        <v>2.106717461552971</v>
       </c>
       <c r="P239" t="n">
-        <v>0.6219843638035434</v>
+        <v>2.417624391032172</v>
       </c>
       <c r="Q239" t="n">
-        <v>0.4361177456485267</v>
+        <v>1.884452312498166</v>
       </c>
     </row>
     <row r="240">
@@ -13631,16 +13631,16 @@
         <v>0.6090734568217319</v>
       </c>
       <c r="N240" t="n">
-        <v>-0.7420454940093754</v>
+        <v>2.514991691509467</v>
       </c>
       <c r="O240" t="n">
-        <v>0.291693462309002</v>
+        <v>2.512321222171304</v>
       </c>
       <c r="P240" t="n">
-        <v>0.8380201659079396</v>
+        <v>3.046417970483927</v>
       </c>
       <c r="Q240" t="n">
-        <v>0.6090734568217319</v>
+        <v>2.2108402286633</v>
       </c>
     </row>
     <row r="241">
@@ -13686,16 +13686,16 @@
         <v>0.1771834087763946</v>
       </c>
       <c r="N241" t="n">
-        <v>-1.82562829443643</v>
+        <v>6.161370885953819</v>
       </c>
       <c r="O241" t="n">
-        <v>-0.4646306318196249</v>
+        <v>2.247564139957263</v>
       </c>
       <c r="P241" t="n">
-        <v>0.1388013047462477</v>
+        <v>2.712597298265005</v>
       </c>
       <c r="Q241" t="n">
-        <v>0.1771834087763946</v>
+        <v>1.967689463906386</v>
       </c>
     </row>
     <row r="242">
@@ -13741,16 +13741,16 @@
         <v>0.0924410154399337</v>
       </c>
       <c r="N242" t="n">
-        <v>0.0821293518740193</v>
+        <v>2.503897822226725</v>
       </c>
       <c r="O242" t="n">
-        <v>0.2048923987767717</v>
+        <v>2.217045658004467</v>
       </c>
       <c r="P242" t="n">
-        <v>0.4874501406724275</v>
+        <v>2.499661521707651</v>
       </c>
       <c r="Q242" t="n">
-        <v>0.0924410154399337</v>
+        <v>1.533223860865657</v>
       </c>
     </row>
     <row r="243">
@@ -13796,16 +13796,16 @@
         <v>1.566142786675458</v>
       </c>
       <c r="N243" t="n">
-        <v>-0.7049538969257393</v>
+        <v>2.919572544834383</v>
       </c>
       <c r="O243" t="n">
-        <v>-0.128591939258928</v>
+        <v>1.379049211036996</v>
       </c>
       <c r="P243" t="n">
-        <v>0.4715718199376728</v>
+        <v>2.159759384331653</v>
       </c>
       <c r="Q243" t="n">
-        <v>1.566142786675458</v>
+        <v>4.873370844264001</v>
       </c>
     </row>
     <row r="244">
@@ -13851,16 +13851,16 @@
         <v>0.4029391886475219</v>
       </c>
       <c r="N244" t="n">
-        <v>-1.20857313248824</v>
+        <v>3.469754166884941</v>
       </c>
       <c r="O244" t="n">
-        <v>0.9767208334564228</v>
+        <v>3.269957470754729</v>
       </c>
       <c r="P244" t="n">
-        <v>1.404690966493327</v>
+        <v>4.709929585358397</v>
       </c>
       <c r="Q244" t="n">
-        <v>0.4029391886475219</v>
+        <v>2.560726898573765</v>
       </c>
     </row>
     <row r="245">
@@ -13906,16 +13906,16 @@
         <v>-0.3391543637398303</v>
       </c>
       <c r="N245" t="n">
-        <v>-1.244990630331095</v>
+        <v>3.13519415602532</v>
       </c>
       <c r="O245" t="n">
-        <v>0.02244704830227539</v>
+        <v>2.164294635190687</v>
       </c>
       <c r="P245" t="n">
-        <v>0.5859311632566508</v>
+        <v>3.114018394269058</v>
       </c>
       <c r="Q245" t="n">
-        <v>-0.3391543637398303</v>
+        <v>2.375009868700555</v>
       </c>
     </row>
     <row r="246">
@@ -13961,16 +13961,16 @@
         <v>1.216653349580439</v>
       </c>
       <c r="N246" t="n">
-        <v>0.6723571144168788</v>
+        <v>2.293627838154886</v>
       </c>
       <c r="O246" t="n">
-        <v>0.6960225678967651</v>
+        <v>2.200200504975887</v>
       </c>
       <c r="P246" t="n">
-        <v>1.325896663062583</v>
+        <v>4.216602173299366</v>
       </c>
       <c r="Q246" t="n">
-        <v>1.216653349580439</v>
+        <v>4.500316979230415</v>
       </c>
     </row>
     <row r="247">
@@ -14016,16 +14016,16 @@
         <v>1.405077683974842</v>
       </c>
       <c r="N247" t="n">
-        <v>0.3834843955272518</v>
+        <v>1.683649840658664</v>
       </c>
       <c r="O247" t="n">
-        <v>0.5381312152426408</v>
+        <v>1.802594196914945</v>
       </c>
       <c r="P247" t="n">
-        <v>1.064786908736923</v>
+        <v>3.377858145454514</v>
       </c>
       <c r="Q247" t="n">
-        <v>1.405077683974842</v>
+        <v>4.721666738700993</v>
       </c>
     </row>
     <row r="248">
@@ -14071,16 +14071,16 @@
         <v>1.748821726469486</v>
       </c>
       <c r="N248" t="n">
-        <v>-0.82736973181637</v>
+        <v>3.316962001850273</v>
       </c>
       <c r="O248" t="n">
-        <v>1.397998436223548</v>
+        <v>3.654205529210819</v>
       </c>
       <c r="P248" t="n">
-        <v>1.265185471701427</v>
+        <v>3.160115500529013</v>
       </c>
       <c r="Q248" t="n">
-        <v>1.748821726469486</v>
+        <v>5.757533459160685</v>
       </c>
     </row>
     <row r="249">
@@ -14126,16 +14126,16 @@
         <v>0.1484012332867924</v>
       </c>
       <c r="N249" t="n">
-        <v>0.3171353407364174</v>
+        <v>1.681384986327171</v>
       </c>
       <c r="O249" t="n">
-        <v>1.604637168405748</v>
+        <v>4.435330976086949</v>
       </c>
       <c r="P249" t="n">
-        <v>1.954452116416675</v>
+        <v>5.770871063963753</v>
       </c>
       <c r="Q249" t="n">
-        <v>0.1484012332867924</v>
+        <v>2.201268052734958</v>
       </c>
     </row>
     <row r="250">
@@ -14181,16 +14181,16 @@
         <v>-0.1454132914341372</v>
       </c>
       <c r="N250" t="n">
-        <v>0.3171353407364174</v>
+        <v>1.681384986327171</v>
       </c>
       <c r="O250" t="n">
-        <v>1.564960766924452</v>
+        <v>4.251431009171789</v>
       </c>
       <c r="P250" t="n">
-        <v>1.865313778675883</v>
+        <v>5.409164420268259</v>
       </c>
       <c r="Q250" t="n">
-        <v>-0.1454132914341372</v>
+        <v>2.087511806035775</v>
       </c>
     </row>
     <row r="251">
@@ -14236,16 +14236,16 @@
         <v>0.09676513368004633</v>
       </c>
       <c r="N251" t="n">
-        <v>0.3171353407364174</v>
+        <v>1.681384986327171</v>
       </c>
       <c r="O251" t="n">
-        <v>1.572603854950154</v>
+        <v>4.347242159327884</v>
       </c>
       <c r="P251" t="n">
-        <v>1.927137169335479</v>
+        <v>5.663455696683446</v>
       </c>
       <c r="Q251" t="n">
-        <v>0.09676513368004633</v>
+        <v>2.106355058224253</v>
       </c>
     </row>
     <row r="252">
@@ -14291,16 +14291,16 @@
         <v>0.4971136304712507</v>
       </c>
       <c r="N252" t="n">
-        <v>1.128677950155612</v>
+        <v>3.243311857917598</v>
       </c>
       <c r="O252" t="n">
-        <v>1.738821414222993</v>
+        <v>6.296194730169435</v>
       </c>
       <c r="P252" t="n">
-        <v>1.368622045323498</v>
+        <v>4.785862517476334</v>
       </c>
       <c r="Q252" t="n">
-        <v>0.4971136304712507</v>
+        <v>2.961063585897179</v>
       </c>
     </row>
     <row r="253">
@@ -14346,16 +14346,16 @@
         <v>0.449847434697877</v>
       </c>
       <c r="N253" t="n">
-        <v>1.133154574971092</v>
+        <v>3.237258069800335</v>
       </c>
       <c r="O253" t="n">
-        <v>1.629226168946553</v>
+        <v>5.977800167398266</v>
       </c>
       <c r="P253" t="n">
-        <v>1.345835247118464</v>
+        <v>4.676055018884602</v>
       </c>
       <c r="Q253" t="n">
-        <v>0.449847434697877</v>
+        <v>2.921995487400804</v>
       </c>
     </row>
     <row r="254">
@@ -14401,16 +14401,16 @@
         <v>1.097511008887493</v>
       </c>
       <c r="N254" t="n">
-        <v>0.07693675835063876</v>
+        <v>1.196559033076563</v>
       </c>
       <c r="O254" t="n">
-        <v>1.215338796875402</v>
+        <v>3.425066666666666</v>
       </c>
       <c r="P254" t="n">
-        <v>1.311671827491933</v>
+        <v>3.734687853061267</v>
       </c>
       <c r="Q254" t="n">
-        <v>1.097511008887493</v>
+        <v>3.137949062835517</v>
       </c>
     </row>
     <row r="255">
@@ -14456,16 +14456,16 @@
         <v>1.542921604807151</v>
       </c>
       <c r="N255" t="n">
-        <v>0.04801276891305795</v>
+        <v>1.157428665270489</v>
       </c>
       <c r="O255" t="n">
-        <v>0.7081003995699293</v>
+        <v>2.00537925667978</v>
       </c>
       <c r="P255" t="n">
-        <v>1.058538778629213</v>
+        <v>3.226238552886132</v>
       </c>
       <c r="Q255" t="n">
-        <v>1.542921604807151</v>
+        <v>4.323448785354926</v>
       </c>
     </row>
     <row r="256">
@@ -14511,16 +14511,16 @@
         <v>1.508371807575261</v>
       </c>
       <c r="N256" t="n">
-        <v>0.04801276891305795</v>
+        <v>1.157428665270489</v>
       </c>
       <c r="O256" t="n">
-        <v>0.6860155876045139</v>
+        <v>1.793623958459123</v>
       </c>
       <c r="P256" t="n">
-        <v>1.145042548109662</v>
+        <v>3.465627497163513</v>
       </c>
       <c r="Q256" t="n">
-        <v>1.508371807575261</v>
+        <v>4.233453149203603</v>
       </c>
     </row>
     <row r="257">
@@ -14566,16 +14566,16 @@
         <v>0.09006326602106542</v>
       </c>
       <c r="N257" t="n">
-        <v>-0.7304797203214838</v>
+        <v>2.75792503162754</v>
       </c>
       <c r="O257" t="n">
-        <v>0.1136352519507512</v>
+        <v>2.097388238953954</v>
       </c>
       <c r="P257" t="n">
-        <v>0.6132438745989008</v>
+        <v>2.271514676996047</v>
       </c>
       <c r="Q257" t="n">
-        <v>0.09006326602106542</v>
+        <v>1.305096078623919</v>
       </c>
     </row>
     <row r="258">
@@ -14621,16 +14621,16 @@
         <v>0.9757551204982924</v>
       </c>
       <c r="N258" t="n">
-        <v>-0.9348584259150732</v>
+        <v>2.441422000937165</v>
       </c>
       <c r="O258" t="n">
-        <v>0.5656408463908079</v>
+        <v>2.639600595071642</v>
       </c>
       <c r="P258" t="n">
-        <v>0.3011610178132368</v>
+        <v>2.24759910393394</v>
       </c>
       <c r="Q258" t="n">
-        <v>0.9757551204982924</v>
+        <v>3.74443159941677</v>
       </c>
     </row>
     <row r="259">
@@ -14676,16 +14676,16 @@
         <v>0.4064643615326924</v>
       </c>
       <c r="N259" t="n">
-        <v>-0.9324461588713968</v>
+        <v>2.443947561527554</v>
       </c>
       <c r="O259" t="n">
-        <v>1.141431114623964</v>
+        <v>4.139019100446504</v>
       </c>
       <c r="P259" t="n">
-        <v>0.548948369112513</v>
+        <v>2.477614927363171</v>
       </c>
       <c r="Q259" t="n">
-        <v>0.4064643615326924</v>
+        <v>2.178150011075801</v>
       </c>
     </row>
     <row r="260">
@@ -14731,16 +14731,16 @@
         <v>0.6730196585984505</v>
       </c>
       <c r="N260" t="n">
-        <v>-0.9362548184792245</v>
+        <v>2.450437384866044</v>
       </c>
       <c r="O260" t="n">
-        <v>1.375997833835897</v>
+        <v>4.970499084748507</v>
       </c>
       <c r="P260" t="n">
-        <v>0.7852455319360339</v>
+        <v>3.084620436456203</v>
       </c>
       <c r="Q260" t="n">
-        <v>0.6730196585984505</v>
+        <v>2.993796418916704</v>
       </c>
     </row>
     <row r="261">
@@ -14786,16 +14786,16 @@
         <v>0.3048134596135526</v>
       </c>
       <c r="N261" t="n">
-        <v>-0.6170619300979481</v>
+        <v>3.254162410208823</v>
       </c>
       <c r="O261" t="n">
-        <v>0.4119605299264684</v>
+        <v>2.363168712919114</v>
       </c>
       <c r="P261" t="n">
-        <v>0.9177608773049282</v>
+        <v>3.192626675552765</v>
       </c>
       <c r="Q261" t="n">
-        <v>0.3048134596135526</v>
+        <v>1.892080890048473</v>
       </c>
     </row>
     <row r="262">
@@ -14841,16 +14841,16 @@
         <v>0.977514769437595</v>
       </c>
       <c r="N262" t="n">
-        <v>-0.3414590616684793</v>
+        <v>1.91872041669139</v>
       </c>
       <c r="O262" t="n">
-        <v>0.5647018802862628</v>
+        <v>2.70888348107029</v>
       </c>
       <c r="P262" t="n">
-        <v>1.273251533031949</v>
+        <v>4.849001521837415</v>
       </c>
       <c r="Q262" t="n">
-        <v>0.977514769437595</v>
+        <v>3.802785226963321</v>
       </c>
     </row>
     <row r="263">
@@ -14896,16 +14896,16 @@
         <v>1.000964762524135</v>
       </c>
       <c r="N263" t="n">
-        <v>-0.619929502066333</v>
+        <v>2.366415333748193</v>
       </c>
       <c r="O263" t="n">
-        <v>0.5355634917353375</v>
+        <v>2.797965110110976</v>
       </c>
       <c r="P263" t="n">
-        <v>1.102278863833382</v>
+        <v>4.195042622807621</v>
       </c>
       <c r="Q263" t="n">
-        <v>1.000964762524135</v>
+        <v>3.951972814104646</v>
       </c>
     </row>
     <row r="264">
@@ -14951,16 +14951,16 @@
         <v>1.211818046429152</v>
       </c>
       <c r="N264" t="n">
-        <v>-0.6294400295309869</v>
+        <v>2.391397104316923</v>
       </c>
       <c r="O264" t="n">
-        <v>0.4462834083391506</v>
+        <v>2.360574395707633</v>
       </c>
       <c r="P264" t="n">
-        <v>0.9522972745615246</v>
+        <v>3.676725311446423</v>
       </c>
       <c r="Q264" t="n">
-        <v>1.211818046429152</v>
+        <v>4.483158503855342</v>
       </c>
     </row>
     <row r="265">
@@ -15006,16 +15006,16 @@
         <v>0.6022803347760699</v>
       </c>
       <c r="N265" t="n">
-        <v>-0.9643350910196571</v>
+        <v>2.67689608031281</v>
       </c>
       <c r="O265" t="n">
-        <v>0.8195756418232309</v>
+        <v>2.599458550533841</v>
       </c>
       <c r="P265" t="n">
-        <v>0.7686042660905927</v>
+        <v>2.569517389257338</v>
       </c>
       <c r="Q265" t="n">
-        <v>0.6022803347760699</v>
+        <v>3.381797664062546</v>
       </c>
     </row>
     <row r="266">
@@ -15061,16 +15061,16 @@
         <v>1.441093929170086</v>
       </c>
       <c r="N266" t="n">
-        <v>-0.8846360175774648</v>
+        <v>2.033797981147181</v>
       </c>
       <c r="O266" t="n">
-        <v>0.121032330586208</v>
+        <v>1.856832</v>
       </c>
       <c r="P266" t="n">
-        <v>1.490469656627106</v>
+        <v>4.904900870937031</v>
       </c>
       <c r="Q266" t="n">
-        <v>1.441093929170086</v>
+        <v>5.134269337222241</v>
       </c>
     </row>
     <row r="267">
@@ -15116,16 +15116,16 @@
         <v>1.497039060156369</v>
       </c>
       <c r="N267" t="n">
-        <v>-0.8846360175774648</v>
+        <v>2.033797981147181</v>
       </c>
       <c r="O267" t="n">
-        <v>0.2240421504629962</v>
+        <v>1.944536640754651</v>
       </c>
       <c r="P267" t="n">
-        <v>1.473160263525229</v>
+        <v>4.82654228437573</v>
       </c>
       <c r="Q267" t="n">
-        <v>1.497039060156369</v>
+        <v>5.247868287065087</v>
       </c>
     </row>
     <row r="268">
@@ -15171,16 +15171,16 @@
         <v>-0.3822068021473402</v>
       </c>
       <c r="N268" t="n">
-        <v>-1.728790651807398</v>
+        <v>4.517725961361471</v>
       </c>
       <c r="O268" t="n">
-        <v>0.3472605553424958</v>
+        <v>2.505912580591156</v>
       </c>
       <c r="P268" t="n">
-        <v>0.6800210267182301</v>
+        <v>2.533662207472627</v>
       </c>
       <c r="Q268" t="n">
-        <v>-0.3822068021473402</v>
+        <v>2.393082214870292</v>
       </c>
     </row>
     <row r="269">
@@ -15226,16 +15226,16 @@
         <v>0.2522964734904924</v>
       </c>
       <c r="N269" t="n">
-        <v>-0.3623161713630573</v>
+        <v>2.016116241188694</v>
       </c>
       <c r="O269" t="n">
-        <v>-0.2537859078400056</v>
+        <v>1.840448452600533</v>
       </c>
       <c r="P269" t="n">
-        <v>0.5873195306417056</v>
+        <v>2.576939358353186</v>
       </c>
       <c r="Q269" t="n">
-        <v>0.2522964734904924</v>
+        <v>2.953252297572283</v>
       </c>
     </row>
     <row r="270">
@@ -15281,16 +15281,16 @@
         <v>-0.1900299561277518</v>
       </c>
       <c r="N270" t="n">
-        <v>-0.3782000056687969</v>
+        <v>2.461582762878299</v>
       </c>
       <c r="O270" t="n">
-        <v>0.4211869316563324</v>
+        <v>2.620387811634349</v>
       </c>
       <c r="P270" t="n">
-        <v>0.2801708306357664</v>
+        <v>2.755187090935169</v>
       </c>
       <c r="Q270" t="n">
-        <v>-0.1900299561277518</v>
+        <v>1.851810034722891</v>
       </c>
     </row>
     <row r="271">
@@ -15336,16 +15336,16 @@
         <v>-0.1815185274104404</v>
       </c>
       <c r="N271" t="n">
-        <v>-0.3782000056687969</v>
+        <v>2.461582762878299</v>
       </c>
       <c r="O271" t="n">
-        <v>0.2794564435892661</v>
+        <v>2.39564897120098</v>
       </c>
       <c r="P271" t="n">
-        <v>0.1923919861801966</v>
+        <v>2.61550254217759</v>
       </c>
       <c r="Q271" t="n">
-        <v>-0.1815185274104404</v>
+        <v>1.862124440250289</v>
       </c>
     </row>
     <row r="272">
@@ -15391,16 +15391,16 @@
         <v>-0.2395562471289732</v>
       </c>
       <c r="N272" t="n">
-        <v>-0.3748614435204386</v>
+        <v>2.450888574524376</v>
       </c>
       <c r="O272" t="n">
-        <v>0.4460266247431054</v>
+        <v>2.294188323246706</v>
       </c>
       <c r="P272" t="n">
-        <v>0.2294439119611121</v>
+        <v>2.62440518036321</v>
       </c>
       <c r="Q272" t="n">
-        <v>-0.2395562471289732</v>
+        <v>1.874078611036874</v>
       </c>
     </row>
     <row r="273">
@@ -15446,16 +15446,16 @@
         <v>1.042579074891132</v>
       </c>
       <c r="N273" t="n">
-        <v>0.4722968036313719</v>
+        <v>2.408627280448444</v>
       </c>
       <c r="O273" t="n">
-        <v>0.8895066546936513</v>
+        <v>2.783669935780341</v>
       </c>
       <c r="P273" t="n">
-        <v>0.9626504553489852</v>
+        <v>2.348624798879758</v>
       </c>
       <c r="Q273" t="n">
-        <v>1.042579074891132</v>
+        <v>3.055119502638305</v>
       </c>
     </row>
     <row r="274">
@@ -15501,16 +15501,16 @@
         <v>0.5085669980861071</v>
       </c>
       <c r="N274" t="n">
-        <v>-0.06394757053245999</v>
+        <v>1.197605778523747</v>
       </c>
       <c r="O274" t="n">
-        <v>1.336506677663831</v>
+        <v>3.515519447308854</v>
       </c>
       <c r="P274" t="n">
-        <v>1.544389056747186</v>
+        <v>4.3858898301032</v>
       </c>
       <c r="Q274" t="n">
-        <v>0.5085669980861071</v>
+        <v>1.972811191329684</v>
       </c>
     </row>
     <row r="275">
@@ -15556,16 +15556,16 @@
         <v>0.001279762609083227</v>
       </c>
       <c r="N275" t="n">
-        <v>-0.9196559810393603</v>
+        <v>2.17939593099606</v>
       </c>
       <c r="O275" t="n">
-        <v>0.4068640967190549</v>
+        <v>1.65589425568463</v>
       </c>
       <c r="P275" t="n">
-        <v>0.5892235160816124</v>
+        <v>1.772982362209354</v>
       </c>
       <c r="Q275" t="n">
-        <v>0.001279762609083227</v>
+        <v>1.592841993641795</v>
       </c>
     </row>
     <row r="276">
@@ -15611,16 +15611,16 @@
         <v>0.007498763906886284</v>
       </c>
       <c r="N276" t="n">
-        <v>-0.9202912454870282</v>
+        <v>2.180106903809988</v>
       </c>
       <c r="O276" t="n">
-        <v>0.4075829826597917</v>
+        <v>1.690089555243705</v>
       </c>
       <c r="P276" t="n">
-        <v>0.6141014706677943</v>
+        <v>1.837812550221274</v>
       </c>
       <c r="Q276" t="n">
-        <v>0.007498763906886284</v>
+        <v>1.60307770212813</v>
       </c>
     </row>
     <row r="277">
@@ -15666,16 +15666,16 @@
         <v>0.5192033434749727</v>
       </c>
       <c r="N277" t="n">
-        <v>0.5026153752718755</v>
+        <v>2.185538765995026</v>
       </c>
       <c r="O277" t="n">
-        <v>0.6987154893320532</v>
+        <v>2.449963233812581</v>
       </c>
       <c r="P277" t="n">
-        <v>0.595982132936352</v>
+        <v>2.378076913033177</v>
       </c>
       <c r="Q277" t="n">
-        <v>0.5192033434749727</v>
+        <v>3.656170610239578</v>
       </c>
     </row>
     <row r="278">
@@ -15721,16 +15721,16 @@
         <v>0.04162845843850786</v>
       </c>
       <c r="N278" t="n">
-        <v>1.14556050286127</v>
+        <v>2.913454205464735</v>
       </c>
       <c r="O278" t="n">
-        <v>0.7298547005426049</v>
+        <v>1.846165545479149</v>
       </c>
       <c r="P278" t="n">
-        <v>0.7207461977973082</v>
+        <v>1.768153992353805</v>
       </c>
       <c r="Q278" t="n">
-        <v>0.04162845843850786</v>
+        <v>1.697142679160806</v>
       </c>
     </row>
     <row r="279">
@@ -15776,16 +15776,16 @@
         <v>1.170524274014861</v>
       </c>
       <c r="N279" t="n">
-        <v>0.193069998321221</v>
+        <v>2.298168181026818</v>
       </c>
       <c r="O279" t="n">
-        <v>0.757132503898046</v>
+        <v>2.637917628605115</v>
       </c>
       <c r="P279" t="n">
-        <v>0.2451078656753386</v>
+        <v>1.59133096398844</v>
       </c>
       <c r="Q279" t="n">
-        <v>1.170524274014861</v>
+        <v>4.555281072804651</v>
       </c>
     </row>
     <row r="280">
@@ -15831,16 +15831,16 @@
         <v>1.221006577613176</v>
       </c>
       <c r="N280" t="n">
-        <v>0.193069998321221</v>
+        <v>2.298168181026818</v>
       </c>
       <c r="O280" t="n">
-        <v>1.33228764469676</v>
+        <v>4.283408890592826</v>
       </c>
       <c r="P280" t="n">
-        <v>0.4790913850687347</v>
+        <v>1.803087887493849</v>
       </c>
       <c r="Q280" t="n">
-        <v>1.221006577613176</v>
+        <v>4.171897133810154</v>
       </c>
     </row>
     <row r="281">
@@ -15886,16 +15886,16 @@
         <v>1.173525694459757</v>
       </c>
       <c r="N281" t="n">
-        <v>0.193069998321221</v>
+        <v>2.298168181026818</v>
       </c>
       <c r="O281" t="n">
-        <v>0.6700836764873154</v>
+        <v>2.459187536296463</v>
       </c>
       <c r="P281" t="n">
-        <v>0.2775992504892078</v>
+        <v>1.598317118897577</v>
       </c>
       <c r="Q281" t="n">
-        <v>1.173525694459757</v>
+        <v>4.471722811755107</v>
       </c>
     </row>
     <row r="282">
@@ -15941,16 +15941,16 @@
         <v>1.546583122149751</v>
       </c>
       <c r="N282" t="n">
-        <v>0.1804589560567808</v>
+        <v>1.176576171957399</v>
       </c>
       <c r="O282" t="n">
-        <v>0.8899174192346065</v>
+        <v>2.76</v>
       </c>
       <c r="P282" t="n">
-        <v>1.318791140540683</v>
+        <v>3.770907037627214</v>
       </c>
       <c r="Q282" t="n">
-        <v>1.546583122149751</v>
+        <v>4.728989719482644</v>
       </c>
     </row>
     <row r="283">
@@ -15996,16 +15996,16 @@
         <v>0.4519468588761383</v>
       </c>
       <c r="N283" t="n">
-        <v>-0.6151582201028918</v>
+        <v>3.748801069280465</v>
       </c>
       <c r="O283" t="n">
-        <v>0.4787097344641981</v>
+        <v>2</v>
       </c>
       <c r="P283" t="n">
-        <v>0.8545204695558776</v>
+        <v>2.329188310004252</v>
       </c>
       <c r="Q283" t="n">
-        <v>0.4519468588761383</v>
+        <v>1.709546633129191</v>
       </c>
     </row>
     <row r="284">
@@ -16051,16 +16051,16 @@
         <v>2.332665323593378</v>
       </c>
       <c r="N284" t="n">
-        <v>1.757124145008148</v>
+        <v>4.448296056459749</v>
       </c>
       <c r="O284" t="n">
-        <v>2.826760505120363</v>
+        <v>9.846665711185281</v>
       </c>
       <c r="P284" t="n">
-        <v>2.867378349987977</v>
+        <v>10.01446023613122</v>
       </c>
       <c r="Q284" t="n">
-        <v>2.332665323593378</v>
+        <v>7.517683226544714</v>
       </c>
     </row>
     <row r="285">
@@ -16106,16 +16106,16 @@
         <v>2.886751343895391</v>
       </c>
       <c r="N285" t="n">
-        <v>0.6544262276372532</v>
+        <v>1.554309294109984</v>
       </c>
       <c r="O285" t="n">
-        <v>2.885660848958207</v>
+        <v>10.0909090909091</v>
       </c>
       <c r="P285" t="n">
-        <v>2.886751345691537</v>
+        <v>10.09090909090909</v>
       </c>
       <c r="Q285" t="n">
-        <v>2.886751343895391</v>
+        <v>10.09090909090909</v>
       </c>
     </row>
     <row r="286">
@@ -16161,7 +16161,7 @@
         <v>0</v>
       </c>
       <c r="N286" t="n">
-        <v>1.30599469274112</v>
+        <v>4.070955179656194</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -16216,16 +16216,16 @@
         <v>2.717456849355788</v>
       </c>
       <c r="N287" t="n">
-        <v>2.320325163854494</v>
+        <v>7.455185065044017</v>
       </c>
       <c r="O287" t="n">
-        <v>1.712664677791176</v>
+        <v>4.2</v>
       </c>
       <c r="P287" t="n">
-        <v>2.717456867319604</v>
+        <v>9.368766049132359</v>
       </c>
       <c r="Q287" t="n">
-        <v>2.717456849355788</v>
+        <v>9.36876604913237</v>
       </c>
     </row>
     <row r="288">
@@ -16271,16 +16271,16 @@
         <v>1.713133476154584</v>
       </c>
       <c r="N288" t="n">
-        <v>2.129212635526221</v>
+        <v>6.467128027681661</v>
       </c>
       <c r="O288" t="n">
-        <v>2.129212635526221</v>
+        <v>6.467128027681661</v>
       </c>
       <c r="P288" t="n">
-        <v>1.869231859910951</v>
+        <v>5.068260817384574</v>
       </c>
       <c r="Q288" t="n">
-        <v>1.713133476154584</v>
+        <v>4.202442679004587</v>
       </c>
     </row>
     <row r="289">
@@ -16326,16 +16326,16 @@
         <v>2.886751343817447</v>
       </c>
       <c r="N289" t="n">
-        <v>2.885660848958207</v>
+        <v>10.0909090909091</v>
       </c>
       <c r="O289" t="n">
-        <v>2.885660848958207</v>
+        <v>10.0909090909091</v>
       </c>
       <c r="P289" t="n">
-        <v>2.886751345681794</v>
+        <v>10.09090909090909</v>
       </c>
       <c r="Q289" t="n">
-        <v>2.886751343817447</v>
+        <v>10.09090909090909</v>
       </c>
     </row>
   </sheetData>
